--- a/docs/xlsx/jobs-2026-09-02.xlsx
+++ b/docs/xlsx/jobs-2026-09-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="646">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1927 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Adult Litter Crew Member (King County)</t>
+  </si>
+  <si>
+    <t>WA State Department of Ecology</t>
+  </si>
+  <si>
+    <t>Federal WA, WA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$21.65 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-adult-litter-crew-member-king-county-federal-wa-washington/3402849366</t>
+  </si>
+  <si>
+    <t>Adult Litter Crew Member (Whatcom/Skagit)</t>
+  </si>
+  <si>
+    <t>Bellingham, WA</t>
+  </si>
+  <si>
+    <t>$20.77 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-adult-litter-crew-member-whatcomskagit-bellingham-washington/7850058676</t>
+  </si>
+  <si>
+    <t>Communications Intern</t>
+  </si>
+  <si>
+    <t>Aldo Leopold Nature Center</t>
+  </si>
+  <si>
+    <t>Monona, WI</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$15 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-communications-intern-monona-wisconsin/1171613401</t>
+  </si>
+  <si>
+    <t>Conifer Nursery Shipping Lead (Grenada Forestry Nursery)</t>
+  </si>
+  <si>
+    <t>Sierra Pacific Industries</t>
+  </si>
+  <si>
+    <t>Grenada, CA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$28.50 per hour</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conifer-nursery-shipping-lead-grenada-forestry-nursery-grenada-california/6552963486</t>
+  </si>
+  <si>
+    <t>Conifer Nursery Shipping Support (Grenada Forestry Nursery)</t>
+  </si>
+  <si>
+    <t>$25.46 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conifer-nursery-shipping-support-grenada-forestry-nursery-grenada-california/4629125592</t>
+  </si>
+  <si>
+    <t>Director of Education and Community Engagment</t>
+  </si>
+  <si>
+    <t>Resource Conservation District of the Santa Monica Mountains</t>
+  </si>
+  <si>
+    <t>Calabasas, CA</t>
+  </si>
+  <si>
+    <t>$46 - $52 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-education-and-community-engagment-calabasas-california/6199307331</t>
+  </si>
+  <si>
+    <t>Director of Waste Recovery</t>
+  </si>
+  <si>
+    <t>I Love A Clean San Diego</t>
+  </si>
+  <si>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>$70,304 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-waste-recovery-san-diego-california/4320694811</t>
+  </si>
+  <si>
+    <t>Director, Water Policy</t>
+  </si>
+  <si>
+    <t>Lincoln Institute of Land Policy</t>
+  </si>
+  <si>
+    <t>Cambridge, MA</t>
+  </si>
+  <si>
+    <t>$150,000 - $170,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-water-policy-cambridge-massachusetts/9951478807</t>
+  </si>
+  <si>
+    <t>Educator</t>
+  </si>
+  <si>
+    <t>Alaska Zoo</t>
+  </si>
+  <si>
+    <t>Anchorage, AK</t>
+  </si>
+  <si>
+    <t>$18 - $20 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-educator-anchorage-alaska/9247959893</t>
+  </si>
+  <si>
+    <t>HAWKs</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>$20 - $25 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-educator-denver-colorado/7677235073</t>
+  </si>
+  <si>
+    <t>Electronic Media Producer Specialist</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$4,300 - $5,779 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-electronic-media-producer-specialist-olympia-washington/6066760025</t>
+  </si>
+  <si>
+    <t>Environmental Scientist Inspector</t>
+  </si>
+  <si>
+    <t>Office of Energy Infrastructure Safety</t>
+  </si>
+  <si>
+    <t>Lakewood, CA</t>
+  </si>
+  <si>
+    <t>$4,418 - $9,321 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-scientist-inspector-lakewood-california/6456821350</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>West Virginia Land Trust</t>
+  </si>
+  <si>
+    <t>Charleston, WV</t>
+  </si>
+  <si>
+    <t>$130,000 - $175,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-charleston-west-virginia/7085994189</t>
+  </si>
+  <si>
+    <t>Farm Manager-Shepard Farm</t>
+  </si>
+  <si>
+    <t>Dodge Nature Center</t>
+  </si>
+  <si>
+    <t>West St. Paul, MN</t>
+  </si>
+  <si>
+    <t>$37,623 - $45,000 per year</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-farm-manager-shepard-farm-west-st-paul-minnesota/8901829159</t>
+  </si>
+  <si>
+    <t>Fellowships and Internships Manager</t>
+  </si>
+  <si>
+    <t>SC Sea Grant Consortium</t>
+  </si>
+  <si>
+    <t>Charleston, SC</t>
+  </si>
+  <si>
+    <t>$45,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fellowships-and-internships-manager-charleston-south-carolina/3810062431</t>
+  </si>
+  <si>
+    <t>Forestry Technician TEMP (Seasonal)</t>
+  </si>
+  <si>
+    <t>Larimer County Sheriff's Office</t>
+  </si>
+  <si>
+    <t>Fort Collins, CO</t>
+  </si>
+  <si>
+    <t>$26.14 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-technician-temp-seasonal-fort-collins-colorado/8745411727</t>
+  </si>
+  <si>
+    <t>Geographic Information Specialist II-III (GIS Analyst)</t>
+  </si>
+  <si>
+    <t>Texas Parks &amp; Wildlife Department</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>$5,442 - $6,481.93 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-geographic-information-specialist-ii-iii-gis-analyst-austin-texas/4401539948</t>
+  </si>
+  <si>
+    <t>Interpretation and Education Intern (NPS, Glen Canyon National Recreation Area)</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Page, AZ</t>
+  </si>
+  <si>
+    <t>$19.00/hr</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-interpretation-and-education-intern-nps-glen-canyon-national-recreation-area-page-arizona/5466572221</t>
+  </si>
+  <si>
+    <t>Native Seed Technician</t>
+  </si>
+  <si>
+    <t>Montana DNRC Conservation Seedling Nursery</t>
+  </si>
+  <si>
+    <t>Missoula, MT</t>
+  </si>
+  <si>
+    <t>botany</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-native-seed-technician-missoula-montana/7771545000</t>
+  </si>
+  <si>
+    <t>Natural Resources Specialist V (Fisheries District Supervisor)</t>
+  </si>
+  <si>
+    <t>San Antonio, TX</t>
+  </si>
+  <si>
+    <t>$7,694.42 per month</t>
+  </si>
+  <si>
+    <t>ecology-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-specialist-v-fisheries-district-supervisor-san-antonio-texas/1865204369</t>
+  </si>
+  <si>
+    <t>Planner II - III (Park Planner - Statewide)</t>
+  </si>
+  <si>
+    <t>$6,025 - $6,699.20 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-planner-ii---iii-park-planner---statewide-austin-texas/5553945957</t>
+  </si>
+  <si>
+    <t>Postdoctoral Researcher in Gray Whale Ecology and Biology</t>
+  </si>
+  <si>
+    <t>University of California Santa Barbara</t>
+  </si>
+  <si>
+    <t>Santa Barbara, CA</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>$71,491 - $85,736 per year</t>
+  </si>
+  <si>
+    <t>ecology-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-postdoctoral-researcher-in-gray-whale-ecology-and-biology-santa-barbara-california/6822451899</t>
+  </si>
+  <si>
+    <t>Principal Associate, Protecting Australia’s Nature</t>
+  </si>
+  <si>
+    <t>Pew Charitable Trusts</t>
+  </si>
+  <si>
+    <t>Brisbane, Australia</t>
+  </si>
+  <si>
+    <t>$115,700 - $129,200 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-principal-associate-protecting-australias-nature-brisbane-australia/7566427671</t>
+  </si>
+  <si>
+    <t>Program Operations Analyst (Operations &amp; Policy Analyst 1)</t>
+  </si>
+  <si>
+    <t>Oregon Department of State Lands</t>
+  </si>
+  <si>
+    <t>Salem, OR</t>
+  </si>
+  <si>
+    <t>$4,519 - $6,900 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-operations-analyst-operations--policy-analyst-1-salem-oregon/6976243346</t>
+  </si>
+  <si>
+    <t>Regulatory Geologist/Hydrologist</t>
+  </si>
+  <si>
+    <t>VESTRA Resources, Inc.</t>
+  </si>
+  <si>
+    <t>Redding, CA</t>
+  </si>
+  <si>
+    <t>$28.85 - $37 per hour</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regulatory-geologisthydrologist-redding-california/4417021500</t>
+  </si>
+  <si>
+    <t>Residential Internships at OAEC</t>
+  </si>
+  <si>
+    <t>Occidental Arts &amp; Ecology Center</t>
+  </si>
+  <si>
+    <t>Occidental, CA</t>
+  </si>
+  <si>
+    <t>$825 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-residential-internships-at-oaec-occidental-california/3248433952</t>
+  </si>
+  <si>
+    <t>Southeast Region Lands Project Manager</t>
+  </si>
+  <si>
+    <t>American Battlefield Trust</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>$70,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-southeast-region-lands-project-manager-washington-dc/7409963237</t>
+  </si>
+  <si>
+    <t>🌍 Líder de Equipo F2F | Donantes Individuales | Turno Mañana o Tarde | CABA</t>
+  </si>
+  <si>
+    <t>Ingeniería Sin Fronteras Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/785154b08f334554bc84d9dd3bb3724a-lider-de-equipo-f2f-donantes-individuales-turno-manana-o-tarde-caba-ingenieria-sin-fronteras-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Academic Tutor – STEM Subjects - Part Time</t>
+  </si>
+  <si>
+    <t>Onward We Learn</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eca82c4936374073b4cfa02f3eb36f7e-academic-tutor-stem-subjects-part-time-onward-we-learn-providence</t>
+  </si>
+  <si>
+    <t>Administrator - CPR Institute</t>
+  </si>
+  <si>
+    <t>CPR Institute</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa46522a7d484621b8cd730a46214810-administrator-cpr-institute-cpr-institute-new-york</t>
+  </si>
+  <si>
+    <t>Adolescent Representation Unit Attorney</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 114000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5a837b9c63f4932ac0bb37757d9ca7c-adolescent-representation-unit-attorney-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
+    <t>Annual Giving Manager (New York)</t>
+  </si>
+  <si>
+    <t>United Board for Christian Higher Education in Asia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c157431249344f4bd5075fd028b2548-annual-giving-manager-new-york-united-board-for-christian-higher-education-in-asia-new-york</t>
+  </si>
+  <si>
+    <t>Arts Education Manager</t>
+  </si>
+  <si>
+    <t>Joe's Movement Emporium/World Arts Focus</t>
+  </si>
+  <si>
+    <t>Suitland-Silver Hill, Maryland</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/031355bdb3ae4a759601a7423dcda679-arts-education-manager-joes-movement-emporiumworld-arts-focus-suitland-silver-hill</t>
+  </si>
+  <si>
+    <t>Asistente administrativo - Medio tiempo</t>
+  </si>
+  <si>
+    <t>Ya Respondiste A.C.</t>
+  </si>
+  <si>
+    <t>Ciudad de México, Ciudad de México, MX</t>
+  </si>
+  <si>
+    <t>MXN 10000.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Hunger Food Security, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7850b7d79644236bae2cbe010f987f5-asistente-administrativo-medio-tiempo-ya-respondiste-ac-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>Springfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 87500.00 - 130595.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/fbd4216211204daf85caaafd33de57ab-assistant-attorney-general-office-of-the-massachusetts-attorney-general-springfield</t>
+  </si>
+  <si>
+    <t>Bilingual Front Desk Receptionist (English/Spanish)</t>
+  </si>
+  <si>
+    <t>Housing Conservation Coordinators, Inc.</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 61790.00 - 116994.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9de6786e98041cd80402cfa45e9cdb9-bilingual-front-desk-receptionist-englishspanish-housing-conservation-coordinators-inc-new-york</t>
+  </si>
+  <si>
+    <t>Biologist - Work with rescued wildlife in the Bolivian Amazon</t>
+  </si>
+  <si>
+    <t>Comunidad Inti Wara Yassi (CIWY)</t>
+  </si>
+  <si>
+    <t>Ascensión de Guarayos, Santa Cruz, BO</t>
+  </si>
+  <si>
+    <t>USD 300.00 - 350.00/month</t>
+  </si>
+  <si>
+    <t>Animals, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/38c9b40ca2674fe086d60f9c005e83ce-biologist-work-with-rescued-wildlife-in-the-bolivian-amazon-comunidad-inti-wara-yassi-ciwy-ascension-de-guarayos</t>
+  </si>
+  <si>
+    <t>Captadores de Socios y Líder de Equipo para Vía Pública en el Departamento de Salto, Uruguay</t>
+  </si>
+  <si>
+    <t>MÉDICOS SIN FRONTERAS LAT</t>
+  </si>
+  <si>
+    <t>Salto, Departamento de Salto, UY</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Health Medicine, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/41782f919a944e458281220fb5c41fe4-captadores-de-socios-y-lider-de-equipo-para-via-publica-en-el-departamento-de-salto-uruguay-medicos-sin-fronteras-lat-salto</t>
+  </si>
+  <si>
+    <t>College and Career Advisor</t>
+  </si>
+  <si>
+    <t>Comprehensive Youth Development</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fd6f84a6b204ebf925a5133602eccd2-college-and-career-advisor-comprehensive-youth-development-new-york</t>
+  </si>
+  <si>
+    <t>Communications and Design Coordinator</t>
+  </si>
+  <si>
+    <t>Detroit Disability Power</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Disability, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca2bd12aa28b4e45a02dbfd1bbb80b32-communications-and-design-coordinator-detroit-disability-power-detroit</t>
+  </si>
+  <si>
+    <t>Development and Partnership Manager</t>
+  </si>
+  <si>
+    <t>Not One More Vet, Inc.</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Health Medicine, Job Workplace, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df799b16b8b648ed8296e324afe22248-development-and-partnership-manager-not-one-more-vet-inc-san-francisco</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Friends Center for Children</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ac7fe60b11747c9a4d450f8dfd0fdc2-development-director-friends-center-for-children-new-haven</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Breakthrough Greater Boston</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 79600.00/year</t>
+  </si>
+  <si>
+    <t>Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/06f1f507ae7840b3bd26e2eaa3d0fe31-development-manager-breakthrough-greater-boston-cambridge</t>
+  </si>
+  <si>
+    <t>Aisling Irish Community Center, Inc.</t>
+  </si>
+  <si>
+    <t>Yonkers, New York</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Immigrants Or Refugees, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3440dd4dbdf444839986a579902816ca-development-manager-aisling-irish-community-center-inc-yonkers</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Women's Money Matters</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ee9090a56ae42af8d1fca177be71ab4-director-of-development-womens-money-matters-boston</t>
+  </si>
+  <si>
+    <t>Director of Development and Communications</t>
+  </si>
+  <si>
+    <t>Mainspring Schools</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf088939a3524b9da68e227375598264-director-of-development-and-communications-mainspring-schools-austin</t>
+  </si>
+  <si>
+    <t>Director of Finance and Operations</t>
+  </si>
+  <si>
+    <t>Institute for Contemporary Psychotherapy</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd2a1cc7b1404f4192cb31b504616682-director-of-finance-and-operations-institute-for-contemporary-psychotherapy-new-york</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>Girls Inc. of Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 86000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42ec3531e40a44359a1cfdb318182b50-director-of-programs-girls-inc-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Director of State Policy</t>
+  </si>
+  <si>
+    <t>MAZON: A Jewish Response to Hunger</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 119000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e52e3aa99fc04e88bf7e9019889f0906-director-of-state-policy-mazon-a-jewish-response-to-hunger-los-angeles</t>
+  </si>
+  <si>
+    <t>Donor Relations Manager</t>
+  </si>
+  <si>
+    <t>Summer Search</t>
+  </si>
+  <si>
+    <t>USD 87389.00 - 93596.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf17096accc6489bac77c1f6bf69d896-donor-relations-manager-summer-search-new-york</t>
+  </si>
+  <si>
+    <t>Education Debt Legal Manager</t>
+  </si>
+  <si>
+    <t>CSSNY</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Financial Literacy Personal Finance, Legal Assistance, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/900c9814a94f4d2e834647eb5e02b1b4-education-debt-legal-manager-cssny-new-york</t>
+  </si>
+  <si>
+    <t>Events and Special Projects Assistant</t>
+  </si>
+  <si>
+    <t>Center for US Global Leadership</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 42000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Hunger Food Security, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a98cef008a4a425a9df4edc6aae405b1-events-and-special-projects-assistant-center-for-us-global-leadership-washington</t>
+  </si>
+  <si>
+    <t>Financial Aid Specialist - Part-time</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/acf708f2c2e14ba499a7a7d8d84bc870-financial-aid-specialist-part-time-onward-we-learn-providence</t>
+  </si>
+  <si>
+    <t>Food Pantry Coordinator</t>
+  </si>
+  <si>
+    <t>A Place To Turn</t>
+  </si>
+  <si>
+    <t>Natick, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b52ca8eaa9294157880fbc991a77b98e-food-pantry-coordinator-a-place-to-turn-natick</t>
+  </si>
+  <si>
+    <t>Get Out The Vote Kansas Phone Banker</t>
+  </si>
+  <si>
+    <t>The Voter Network</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 50.00/day</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/22d13e53452e48d58e5cd1215005bb3f-get-out-the-vote-kansas-phone-banker-the-voter-network-kansas-city</t>
+  </si>
+  <si>
+    <t>Global Health Fellow</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Economic Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/226f1f475b9946d0b051469ed3576bde-global-health-fellow-center-for-us-global-leadership-washington</t>
+  </si>
+  <si>
+    <t>Grants, Partnerships &amp; Development Manager</t>
+  </si>
+  <si>
+    <t>Techrity Innovation Foundation</t>
+  </si>
+  <si>
+    <t>Remote (NG)</t>
+  </si>
+  <si>
+    <t>NGN 100000.00 - 100000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa64a55b43394b3191e00a06a7db2085-grants-partnerships-development-manager-techrity-innovation-foundation-port-harcourt</t>
+  </si>
+  <si>
+    <t>Graphic Designer</t>
+  </si>
+  <si>
+    <t>CaringKind, The Heart of Alzheimer’s Caregiving</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Mental Health, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/868e19405f6d4f1288c2a62e40801605-graphic-designer-caringkind-the-heart-of-alzheimers-caregiving-new-york</t>
+  </si>
+  <si>
+    <t>Health Attorney</t>
+  </si>
+  <si>
+    <t>USD 93393.00 - 93393.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Legal Assistance, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b30f3bb1232a4c43a621013b267263b1-health-attorney-cssny-new-york</t>
+  </si>
+  <si>
+    <t>Housing and Human Services Policy Analyst</t>
+  </si>
+  <si>
+    <t>Massachusetts Budget and Policy Center</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 79673.00 - 89764.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Poverty, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/777de003985e46b8b1c2b1acc1dcaf2c-housing-and-human-services-policy-analyst-massachusetts-budget-and-policy-center-boston</t>
+  </si>
+  <si>
+    <t>HR &amp; Office Coordinator</t>
+  </si>
+  <si>
+    <t>PaintCare &amp; American Coatings Association</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9958180699fd43c5ae06439a9d8992e2-hr-office-coordinator-paintcare-american-coatings-association-washington</t>
+  </si>
+  <si>
+    <t>Human Resources Generalist</t>
+  </si>
+  <si>
+    <t>EcoTarium</t>
+  </si>
+  <si>
+    <t>Worcester, MA</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75ba1d4bc186431aa5e6efc86c287663-human-resources-generalist-ecotarium-worcester</t>
+  </si>
+  <si>
+    <t>Immigrant Rights and Worker Justice Organizer</t>
+  </si>
+  <si>
+    <t>Escucha Mi Voz Iowa</t>
+  </si>
+  <si>
+    <t>Iowa City, Iowa</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a72c1ab3f56c4a7cb54433ab10f3de45-immigrant-rights-and-worker-justice-organizer-escucha-mi-voz-iowa-iowa-city</t>
+  </si>
+  <si>
+    <t>In-Home Counselor/Social Worker (serving Baxter, Boone, and Marion counties)</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Deer, Arkansas</t>
+  </si>
+  <si>
+    <t>USD 51000.00 - 59000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbb3040f72c3470a98b1d14ca66dade2-in-home-counselorsocial-worker-serving-baxter-boone-and-marion-counties-youth-villages-deer</t>
+  </si>
+  <si>
+    <t>Mountain Home, Arkansas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a60259835afd4d72b6ebb85eb3d9b3bf-in-home-counselorsocial-worker-serving-baxter-boone-and-marion-counties-youth-villages-mountain-home</t>
+  </si>
+  <si>
+    <t>Junior Accountant</t>
+  </si>
+  <si>
+    <t>True Ground Housing Partners</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0bf0d40b8aba4ecc897d9558d7198574-junior-accountant-true-ground-housing-partners-arlington</t>
+  </si>
+  <si>
+    <t>Legal Counsel</t>
+  </si>
+  <si>
+    <t>Teamsters Local Union No. 705</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68759534e076453bb20ded0943baea85-legal-counsel-teamsters-local-union-no-705-chicago</t>
+  </si>
+  <si>
+    <t>Legal Services Director</t>
+  </si>
+  <si>
+    <t>Asian Law Caucus</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 139050.00 - 176144.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e3cb71fdba824106a9fc266ee2d91b3f-legal-services-director-asian-law-caucus-san-francisco</t>
+  </si>
+  <si>
+    <t>Manager, Summer Math Enrichment (Hyrbid - Los Angeles)</t>
+  </si>
+  <si>
+    <t>The Art of Problem Solving Initiative, Inc.</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 78375.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef0b72a1591b4359987bcdb4344b25cc-manager-summer-math-enrichment-hyrbid-los-angeles-the-art-of-problem-solving-initiative-inc-los-angeles</t>
+  </si>
+  <si>
+    <t>Managing Attorney</t>
+  </si>
+  <si>
+    <t>Church World Service New York</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>USD 75200.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d664db3b1c41404fbbfad85f90dd10ce-managing-attorney-church-world-service-new-york-dallas</t>
+  </si>
+  <si>
+    <t>Network Development &amp; National Initiatives Director</t>
+  </si>
+  <si>
+    <t>Council on American-Islamic Relations - National Headquarters</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 116000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d74350a358e34db6a31e68a5b5c35d12-network-development-national-initiatives-director-council-on-american-islamic-relations-national-headquarters-washington</t>
+  </si>
+  <si>
+    <t>Outreach Director – Western Region</t>
+  </si>
+  <si>
+    <t>Remote (Oklahoma)</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Economic Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0256661627b34185876fdc4b91970c82-outreach-director-western-region-center-for-us-global-leadership-washington</t>
+  </si>
+  <si>
+    <t>Paralegal, LEAP</t>
+  </si>
+  <si>
+    <t>RiseBoro Community Partnership</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 30.22 - 35.72/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2c8f0ad07e240a78629187b22cb9780-paralegal-leap-riseboro-community-partnership-kings-county</t>
+  </si>
+  <si>
+    <t>Payroll &amp; Benefits Specialist</t>
+  </si>
+  <si>
+    <t>National Dance Institute</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1914269f61244938a290ae1a55aa0503-payroll-benefits-specialist-national-dance-institute-new-york</t>
+  </si>
+  <si>
+    <t>Philanthropy Systems Manager</t>
+  </si>
+  <si>
+    <t>New Hampshire Charitable Foundation</t>
+  </si>
+  <si>
+    <t>Concord, New Hampshire</t>
+  </si>
+  <si>
+    <t>USD 78218.00 - 83981.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a0a303306ee4fe58e5ea27fbc6f7fb6-philanthropy-systems-manager-new-hampshire-charitable-foundation-concord</t>
+  </si>
+  <si>
+    <t>Policy Research Specialist</t>
+  </si>
+  <si>
+    <t>FreeFrom</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Legal Assistance, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4fe940538899432aad8993707aeaca23-policy-research-specialist-freefrom-los-angeles</t>
+  </si>
+  <si>
+    <t>Program Assistant</t>
+  </si>
+  <si>
+    <t>National Network for Safe Communities</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7eea95943804c589f625091e056a666-program-assistant-national-network-for-safe-communities-new-york</t>
+  </si>
+  <si>
+    <t>Program Associate, Finance and Engagement</t>
+  </si>
+  <si>
+    <t>National Association of City Transportation Officials (NACTO)</t>
+  </si>
+  <si>
+    <t>USD 68300.00 - 75800.00/year</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/38503ed94650493abedf46251f45c220-program-associate-finance-and-engagement-national-association-of-city-transportation-officials-nacto-new-york</t>
+  </si>
+  <si>
+    <t>Program Associate, Restorative Justice</t>
+  </si>
+  <si>
+    <t>New York Peace Institute</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5a42ec8bd7e44ccb8456826653331204-program-associate-restorative-justice-new-york-peace-institute-new-york</t>
+  </si>
+  <si>
+    <t>Program Mentor ( Part-Time)</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34c219e0d086409593070965920a151d-program-mentor-part-time-onward-we-learn-providence</t>
+  </si>
+  <si>
+    <t>Project Coordinator</t>
+  </si>
+  <si>
+    <t>AHSHAY</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 81000.00 - 86000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c249fa010f414ed88e8710770df4d4ab-project-coordinator-ahshay-seattle</t>
+  </si>
+  <si>
+    <t>Resident Services Coordinator - The Exchange</t>
+  </si>
+  <si>
+    <t>Vienna, Virginia</t>
+  </si>
+  <si>
+    <t>USD 57200.00 - 76300.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a734a4d2264540ee8931f830bec8d3ae-resident-services-coordinator-the-exchange-true-ground-housing-partners-vienna</t>
+  </si>
+  <si>
+    <t>Residential Life Mentor</t>
+  </si>
+  <si>
+    <t>Boys Home of Virginia</t>
+  </si>
+  <si>
+    <t>Covington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 30000.00 - 32000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3fe294be722c4d21a0d5ae8132dd3042-residential-life-mentor-boys-home-of-virginia-covington</t>
+  </si>
+  <si>
+    <t>Senior Manager of Major Gifts</t>
+  </si>
+  <si>
+    <t>Girl Scouts of Connecticut Inc</t>
+  </si>
+  <si>
+    <t>North Haven, CT</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c222a9e9d7e14708ab709cde7620b97c-senior-manager-of-major-gifts-girl-scouts-of-connecticut-inc-north-haven</t>
+  </si>
+  <si>
+    <t>Special Litigation Counsel: Albany Litigation Bureau (3908)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 87356.00 - 186493.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/bda6cc45da09469a815a82adb92e8f9d-special-litigation-counsel-albany-litigation-bureau-3908-new-york-state-office-of-the-attorney-general-albany</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Sanctuary of the South</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/629b2395e97741dfb1d2f6b08ac59a2a-staff-attorney-sanctuary-of-the-south-chattanooga</t>
+  </si>
+  <si>
+    <t>State Policy &amp; Advocacy Specialist</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2cef0a78d59845f59a309ab7fe7b5676-state-policy-advocacy-specialist-freefrom-los-angeles</t>
+  </si>
+  <si>
+    <t>Stop Data Centers Organizing Fellow</t>
+  </si>
+  <si>
+    <t>Food &amp; Water Watch</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96e0e52c710c48c1b1bbb5c84095de64-stop-data-centers-organizing-fellow-food-water-watch-bakersfield</t>
+  </si>
+  <si>
+    <t>Trial Attorney</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/619dbabc784d4bd3931fcdfea3246bc6-trial-attorney-council-on-american-islamic-relations-national-headquarters-washington</t>
+  </si>
+  <si>
+    <t>US Habitat Restoration Project Manager</t>
+  </si>
+  <si>
+    <t>Atlantic Salmon Federation</t>
+  </si>
+  <si>
+    <t>Brunswick, Maine</t>
+  </si>
+  <si>
+    <t>USD 64400.00 - 96600.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Environment, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/76a710d837694ecdad4aa22b40219a50-us-habitat-restoration-project-manager-atlantic-salmon-federation-brunswick</t>
+  </si>
+  <si>
+    <t>VP, Finance and Accounting</t>
+  </si>
+  <si>
+    <t>Inclusiv</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f8d95c3beb641039ac6facef0cb3ad2-vp-finance-and-accounting-inclusiv-kings-county</t>
+  </si>
+  <si>
+    <t>WBA-WBF Administrative Specialist</t>
+  </si>
+  <si>
+    <t>Women's Bar Foundation of Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40500.00/year</t>
+  </si>
+  <si>
+    <t>Family, Legal Assistance, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/00b6eccdc68f425c81339c3a506e445a-wba-wbf-administrative-specialist-womens-bar-foundation-of-massachusetts-boston</t>
+  </si>
+  <si>
+    <t>Youth Development Specialist - Bridge To Wellness</t>
+  </si>
+  <si>
+    <t>Identity, Inc.</t>
+  </si>
+  <si>
+    <t>Gaithersburg, Maryland</t>
+  </si>
+  <si>
+    <t>USD 23.08 - 23.08/hour</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0789dcd75c4b4e2ca1316887fae04ec3-youth-development-specialist-bridge-to-wellness-identity-inc-gaithersburg</t>
+  </si>
+  <si>
+    <t>4-H YOUTH DEVELOPMENT COMMUNITY EDUCATION SPECIALIST</t>
+  </si>
+  <si>
+    <t>University of California Agriculture and Natural Resources</t>
+  </si>
+  <si>
+    <t>Red Bluff, California</t>
+  </si>
+  <si>
+    <t>Program Operations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72825991</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE ASSISTANT 2</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72827213</t>
+  </si>
+  <si>
+    <t>AGRICULTURE MARKET TEAM LEADER</t>
+  </si>
+  <si>
+    <t>Mississippi Department of Agriculture</t>
+  </si>
+  <si>
+    <t>Hinds County, Mississippi</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72838211</t>
+  </si>
+  <si>
+    <t>ASSOCIATE VICE PRESIDENT OF THE OKLAHOMA COOPERATIVE EXTENSION SERVICE</t>
+  </si>
+  <si>
+    <t>Oklahoma State University Extension</t>
+  </si>
+  <si>
+    <t>Stillwater, Oklahoma</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72836989</t>
+  </si>
+  <si>
+    <t>BLACK CREEK COMMUNITY FARM LEAD</t>
+  </si>
+  <si>
+    <t>Black Creek Community Farm</t>
+  </si>
+  <si>
+    <t>Toronto, Ontario</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72851653</t>
+  </si>
+  <si>
+    <t>CALIFORNIA WATER RESOURCE SPECIALIST</t>
+  </si>
+  <si>
+    <t>American Farmland Trust</t>
+  </si>
+  <si>
+    <t>San Joaquin, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72822325</t>
+  </si>
+  <si>
+    <t>CLIENT DEVELOPMENT CATALYST</t>
+  </si>
+  <si>
+    <t>Non GMO Project</t>
+  </si>
+  <si>
+    <t>Bellingham, Washington</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72814993</t>
+  </si>
+  <si>
+    <t>COMMERCIAL FISHERIES AND SEAFOOD EXTENSION SPECIALIST</t>
+  </si>
+  <si>
+    <t>TEXAS SEA GRANT - Texas A and M University</t>
+  </si>
+  <si>
+    <t>Galveston, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72823547</t>
+  </si>
+  <si>
+    <t>COMMUNITY AND ALUMNI ENGAGEMENT MANAGER</t>
+  </si>
+  <si>
+    <t>FoodCorps</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72819881</t>
+  </si>
+  <si>
+    <t>COMMUNITY ENGAGEMENT COORDINATOR</t>
+  </si>
+  <si>
+    <t>PART-TIME - Geniune Foods</t>
+  </si>
+  <si>
+    <t>Gretna, Louisiana</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72832101</t>
+  </si>
+  <si>
+    <t>COMMUNITY ENGAGEMENT MANAGER</t>
+  </si>
+  <si>
+    <t>Harvesters Community Food Network</t>
+  </si>
+  <si>
+    <t>Lawrence, Kansas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72854097</t>
+  </si>
+  <si>
+    <t>COMMUNITY FOOD PROGRAM ASSOCIATE</t>
+  </si>
+  <si>
+    <t>A Place to Turn</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72843099</t>
+  </si>
+  <si>
+    <t>CONTROLLER</t>
+  </si>
+  <si>
+    <t>KC Can Compost</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72852875</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT DIRECTOR</t>
+  </si>
+  <si>
+    <t>McDowell Local Food Advisory Council</t>
+  </si>
+  <si>
+    <t>Marion, North Carolina</t>
+  </si>
+  <si>
+    <t>Fund Development</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72841877</t>
+  </si>
+  <si>
+    <t>DIRECTOR</t>
+  </si>
+  <si>
+    <t>WATER POLICY - Lincoln Institute of Land Policy</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona</t>
+  </si>
+  <si>
+    <t>Policy &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72830879</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF AGRICULTURE</t>
+  </si>
+  <si>
+    <t>CitySeed</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72846765</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF COMMUNITY STRATEGIES</t>
+  </si>
+  <si>
+    <t>The Ford Family Foundation</t>
+  </si>
+  <si>
+    <t>This field-based position must be currently based</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72813771</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF PEOPLE AND OPERATIONS</t>
+  </si>
+  <si>
+    <t>Hunger Free Vermont</t>
+  </si>
+  <si>
+    <t>South Burlington, Vermont</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72818659</t>
+  </si>
+  <si>
+    <t>EXTENSION AGENT FOR FAMILY AND CONSUMER SCIENCES</t>
+  </si>
+  <si>
+    <t>MUHLENBERG COUNTY - University of Kentucky</t>
+  </si>
+  <si>
+    <t>Central City, Kentucky</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72828435</t>
+  </si>
+  <si>
+    <t>EXTENSION ASSISTANT FOR 4-H YOUTH DEVELOPMENT- ADAIR COUNTY</t>
+  </si>
+  <si>
+    <t>University of Kentucky</t>
+  </si>
+  <si>
+    <t>Columbia, Kentucky</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72829657</t>
+  </si>
+  <si>
+    <t>FINANCE DIRECTOR</t>
+  </si>
+  <si>
+    <t>Mad Agriculture</t>
+  </si>
+  <si>
+    <t>Remote with a preference for Boulder, CO headquart</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72834545</t>
+  </si>
+  <si>
+    <t>FOOD EDUCATION PROGRAM COORDINATOR</t>
+  </si>
+  <si>
+    <t>Working Landscapes</t>
+  </si>
+  <si>
+    <t>Warrenton, North Carolina</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72839433</t>
+  </si>
+  <si>
+    <t>FOOD HUB ASSOCIATE</t>
+  </si>
+  <si>
+    <t>FOOTHILLS FOOD HUB - McDowell Local Food Advisory Council</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72840655</t>
+  </si>
+  <si>
+    <t>FOOD RECOVERY OPERATIONS COORDINATOR</t>
+  </si>
+  <si>
+    <t>ExtraFood</t>
+  </si>
+  <si>
+    <t>Kentfield, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72844321</t>
+  </si>
+  <si>
+    <t>FOOD SAFETY FACILITATIES AND OPERATIONS MANAGER</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72855319</t>
+  </si>
+  <si>
+    <t>GARDEN EDUCATION COORDINATOR</t>
+  </si>
+  <si>
+    <t>Auburn, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72824769</t>
+  </si>
+  <si>
+    <t>MANAGER OF ADMINISTRATION AND EVENTS</t>
+  </si>
+  <si>
+    <t>FarmSTAND</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72850431</t>
+  </si>
+  <si>
+    <t>MARKETING AND COMMUNITY ENGAGEMENT SPECIALIST</t>
+  </si>
+  <si>
+    <t>Food Connects</t>
+  </si>
+  <si>
+    <t>Brattleboro, Vermont</t>
+  </si>
+  <si>
+    <t>Communications &amp; Outreach</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72860207</t>
+  </si>
+  <si>
+    <t>PARALEGAL</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72849209</t>
+  </si>
+  <si>
+    <t>PART TIME FOOD SYSTEMS ASSISTANT</t>
+  </si>
+  <si>
+    <t>Riverdale Neighborhood House</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72857763</t>
+  </si>
+  <si>
+    <t>PLATE TO PLANET PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>Make Food Not Waste</t>
+  </si>
+  <si>
+    <t>Detroit Metro, Michigan</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72833323</t>
+  </si>
+  <si>
+    <t>PROGRAM COORDINATOR</t>
+  </si>
+  <si>
+    <t>FOOD AND ACTIVITY AND NUTRITION INITIATIVES - Lurie Childrens Hospital</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72835767</t>
+  </si>
+  <si>
+    <t>PROGRAM DRIVER II</t>
+  </si>
+  <si>
+    <t>The Food Group</t>
+  </si>
+  <si>
+    <t>New Hope, Minnesota</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72845543</t>
+  </si>
+  <si>
+    <t>SANCTUARY KITCHEN CHEF</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72847987</t>
+  </si>
+  <si>
+    <t>SOCIAL MEDIA LEAD</t>
+  </si>
+  <si>
+    <t>Fishwife</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72816215</t>
+  </si>
+  <si>
+    <t>SPECIALIST</t>
+  </si>
+  <si>
+    <t>SENIOR HUNGER PROGRAMS DC REGION - Capital Area Food Bank</t>
+  </si>
+  <si>
+    <t>Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72817437</t>
+  </si>
+  <si>
+    <t>STORYTELLING MANAGER</t>
+  </si>
+  <si>
+    <t>Not Stated, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72821103</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1968,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1994,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2376,658 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" t="s">
+        <v>116</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" t="s">
+        <v>127</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" t="s">
+        <v>133</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" t="s">
+        <v>143</v>
+      </c>
+      <c r="F26" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" t="s">
+        <v>156</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3083,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3122,1594 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F5" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" t="s">
+        <v>199</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F11" t="s">
+        <v>216</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D12" t="s">
+        <v>221</v>
+      </c>
+      <c r="E12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F12" t="s">
+        <v>222</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" t="s">
+        <v>225</v>
+      </c>
+      <c r="C13" t="s">
+        <v>208</v>
+      </c>
+      <c r="D13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" t="s">
+        <v>226</v>
+      </c>
+      <c r="F13" t="s">
+        <v>227</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D14" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14" t="s">
+        <v>232</v>
+      </c>
+      <c r="F14" t="s">
+        <v>233</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D15" t="s">
+        <v>180</v>
+      </c>
+      <c r="E15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" t="s">
+        <v>238</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" t="s">
+        <v>241</v>
+      </c>
+      <c r="C16" t="s">
+        <v>242</v>
+      </c>
+      <c r="D16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" t="s">
+        <v>243</v>
+      </c>
+      <c r="F16" t="s">
+        <v>244</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>246</v>
+      </c>
+      <c r="B17" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" t="s">
+        <v>180</v>
+      </c>
+      <c r="E17" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>246</v>
+      </c>
+      <c r="B18" t="s">
+        <v>252</v>
+      </c>
+      <c r="C18" t="s">
+        <v>253</v>
+      </c>
+      <c r="D18" t="s">
+        <v>180</v>
+      </c>
+      <c r="E18" t="s">
+        <v>254</v>
+      </c>
+      <c r="F18" t="s">
+        <v>255</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B19" t="s">
+        <v>258</v>
+      </c>
+      <c r="C19" t="s">
+        <v>259</v>
+      </c>
+      <c r="D19" t="s">
+        <v>180</v>
+      </c>
+      <c r="E19" t="s">
+        <v>260</v>
+      </c>
+      <c r="F19" t="s">
+        <v>261</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>263</v>
+      </c>
+      <c r="B20" t="s">
+        <v>264</v>
+      </c>
+      <c r="C20" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" t="s">
+        <v>180</v>
+      </c>
+      <c r="E20" t="s">
+        <v>266</v>
+      </c>
+      <c r="F20" t="s">
+        <v>244</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>268</v>
+      </c>
+      <c r="B21" t="s">
+        <v>269</v>
+      </c>
+      <c r="C21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D21" t="s">
+        <v>180</v>
+      </c>
+      <c r="E21" t="s">
+        <v>270</v>
+      </c>
+      <c r="F21" t="s">
+        <v>271</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>273</v>
+      </c>
+      <c r="B22" t="s">
+        <v>274</v>
+      </c>
+      <c r="C22" t="s">
+        <v>275</v>
+      </c>
+      <c r="D22" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" t="s">
+        <v>163</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>278</v>
+      </c>
+      <c r="B23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" t="s">
+        <v>275</v>
+      </c>
+      <c r="D23" t="s">
+        <v>180</v>
+      </c>
+      <c r="E23" t="s">
+        <v>280</v>
+      </c>
+      <c r="F23" t="s">
+        <v>281</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>283</v>
+      </c>
+      <c r="B24" t="s">
+        <v>284</v>
+      </c>
+      <c r="C24" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" t="s">
+        <v>180</v>
+      </c>
+      <c r="E24" t="s">
+        <v>285</v>
+      </c>
+      <c r="F24" t="s">
+        <v>286</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>288</v>
+      </c>
+      <c r="B25" t="s">
+        <v>289</v>
+      </c>
+      <c r="C25" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" t="s">
+        <v>180</v>
+      </c>
+      <c r="E25" t="s">
+        <v>290</v>
+      </c>
+      <c r="F25" t="s">
+        <v>291</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>293</v>
+      </c>
+      <c r="B26" t="s">
+        <v>294</v>
+      </c>
+      <c r="C26" t="s">
+        <v>295</v>
+      </c>
+      <c r="D26" t="s">
+        <v>180</v>
+      </c>
+      <c r="E26" t="s">
+        <v>296</v>
+      </c>
+      <c r="F26" t="s">
+        <v>297</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>299</v>
+      </c>
+      <c r="B27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" t="s">
+        <v>300</v>
+      </c>
+      <c r="F27" t="s">
+        <v>163</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>302</v>
+      </c>
+      <c r="B28" t="s">
+        <v>303</v>
+      </c>
+      <c r="C28" t="s">
+        <v>304</v>
+      </c>
+      <c r="D28" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" t="s">
+        <v>305</v>
+      </c>
+      <c r="F28" t="s">
+        <v>306</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>308</v>
+      </c>
+      <c r="B29" t="s">
+        <v>309</v>
+      </c>
+      <c r="C29" t="s">
+        <v>237</v>
+      </c>
+      <c r="D29" t="s">
+        <v>221</v>
+      </c>
+      <c r="E29" t="s">
+        <v>310</v>
+      </c>
+      <c r="F29" t="s">
+        <v>311</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>313</v>
+      </c>
+      <c r="B30" t="s">
+        <v>294</v>
+      </c>
+      <c r="C30" t="s">
+        <v>295</v>
+      </c>
+      <c r="D30" t="s">
+        <v>180</v>
+      </c>
+      <c r="E30" t="s">
+        <v>314</v>
+      </c>
+      <c r="F30" t="s">
+        <v>315</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>317</v>
+      </c>
+      <c r="B31" t="s">
+        <v>318</v>
+      </c>
+      <c r="C31" t="s">
+        <v>319</v>
+      </c>
+      <c r="D31" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" t="s">
+        <v>320</v>
+      </c>
+      <c r="F31" t="s">
+        <v>321</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>323</v>
+      </c>
+      <c r="B32" t="s">
+        <v>324</v>
+      </c>
+      <c r="C32" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" t="s">
+        <v>180</v>
+      </c>
+      <c r="E32" t="s">
+        <v>325</v>
+      </c>
+      <c r="F32" t="s">
+        <v>326</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>328</v>
+      </c>
+      <c r="B33" t="s">
+        <v>289</v>
+      </c>
+      <c r="C33" t="s">
+        <v>173</v>
+      </c>
+      <c r="D33" t="s">
+        <v>180</v>
+      </c>
+      <c r="E33" t="s">
+        <v>329</v>
+      </c>
+      <c r="F33" t="s">
+        <v>330</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>332</v>
+      </c>
+      <c r="B34" t="s">
+        <v>333</v>
+      </c>
+      <c r="C34" t="s">
+        <v>334</v>
+      </c>
+      <c r="D34" t="s">
+        <v>180</v>
+      </c>
+      <c r="E34" t="s">
+        <v>335</v>
+      </c>
+      <c r="F34" t="s">
+        <v>336</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>338</v>
+      </c>
+      <c r="B35" t="s">
+        <v>339</v>
+      </c>
+      <c r="C35" t="s">
+        <v>295</v>
+      </c>
+      <c r="D35" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" t="s">
+        <v>340</v>
+      </c>
+      <c r="F35" t="s">
+        <v>341</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>343</v>
+      </c>
+      <c r="B36" t="s">
+        <v>344</v>
+      </c>
+      <c r="C36" t="s">
+        <v>345</v>
+      </c>
+      <c r="D36" t="s">
+        <v>180</v>
+      </c>
+      <c r="E36" t="s">
+        <v>340</v>
+      </c>
+      <c r="F36" t="s">
+        <v>346</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>348</v>
+      </c>
+      <c r="B37" t="s">
+        <v>349</v>
+      </c>
+      <c r="C37" t="s">
+        <v>350</v>
+      </c>
+      <c r="D37" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" t="s">
+        <v>351</v>
+      </c>
+      <c r="F37" t="s">
+        <v>352</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>354</v>
+      </c>
+      <c r="B38" t="s">
+        <v>355</v>
+      </c>
+      <c r="C38" t="s">
+        <v>356</v>
+      </c>
+      <c r="D38" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" t="s">
+        <v>357</v>
+      </c>
+      <c r="F38" t="s">
+        <v>358</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>354</v>
+      </c>
+      <c r="B39" t="s">
+        <v>355</v>
+      </c>
+      <c r="C39" t="s">
+        <v>360</v>
+      </c>
+      <c r="D39" t="s">
+        <v>180</v>
+      </c>
+      <c r="E39" t="s">
+        <v>357</v>
+      </c>
+      <c r="F39" t="s">
+        <v>358</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>362</v>
+      </c>
+      <c r="B40" t="s">
+        <v>363</v>
+      </c>
+      <c r="C40" t="s">
+        <v>364</v>
+      </c>
+      <c r="D40" t="s">
+        <v>180</v>
+      </c>
+      <c r="E40" t="s">
+        <v>365</v>
+      </c>
+      <c r="F40" t="s">
+        <v>366</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>368</v>
+      </c>
+      <c r="B41" t="s">
+        <v>369</v>
+      </c>
+      <c r="C41" t="s">
+        <v>370</v>
+      </c>
+      <c r="D41" t="s">
+        <v>180</v>
+      </c>
+      <c r="E41" t="s">
+        <v>371</v>
+      </c>
+      <c r="F41" t="s">
+        <v>372</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>374</v>
+      </c>
+      <c r="B42" t="s">
+        <v>375</v>
+      </c>
+      <c r="C42" t="s">
+        <v>376</v>
+      </c>
+      <c r="D42" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" t="s">
+        <v>377</v>
+      </c>
+      <c r="F42" t="s">
+        <v>378</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>380</v>
+      </c>
+      <c r="B43" t="s">
+        <v>381</v>
+      </c>
+      <c r="C43" t="s">
+        <v>275</v>
+      </c>
+      <c r="D43" t="s">
+        <v>180</v>
+      </c>
+      <c r="E43" t="s">
+        <v>382</v>
+      </c>
+      <c r="F43" t="s">
+        <v>187</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>384</v>
+      </c>
+      <c r="B44" t="s">
+        <v>385</v>
+      </c>
+      <c r="C44" t="s">
+        <v>386</v>
+      </c>
+      <c r="D44" t="s">
+        <v>180</v>
+      </c>
+      <c r="E44" t="s">
+        <v>387</v>
+      </c>
+      <c r="F44" t="s">
+        <v>388</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>390</v>
+      </c>
+      <c r="B45" t="s">
+        <v>391</v>
+      </c>
+      <c r="C45" t="s">
+        <v>237</v>
+      </c>
+      <c r="D45" t="s">
+        <v>180</v>
+      </c>
+      <c r="E45" t="s">
+        <v>392</v>
+      </c>
+      <c r="F45" t="s">
+        <v>393</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>395</v>
+      </c>
+      <c r="B46" t="s">
+        <v>294</v>
+      </c>
+      <c r="C46" t="s">
+        <v>396</v>
+      </c>
+      <c r="D46" t="s">
+        <v>180</v>
+      </c>
+      <c r="E46" t="s">
+        <v>397</v>
+      </c>
+      <c r="F46" t="s">
+        <v>398</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>400</v>
+      </c>
+      <c r="B47" t="s">
+        <v>401</v>
+      </c>
+      <c r="C47" t="s">
+        <v>402</v>
+      </c>
+      <c r="D47" t="s">
+        <v>180</v>
+      </c>
+      <c r="E47" t="s">
+        <v>403</v>
+      </c>
+      <c r="F47" t="s">
+        <v>404</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>406</v>
+      </c>
+      <c r="B48" t="s">
+        <v>407</v>
+      </c>
+      <c r="C48" t="s">
+        <v>208</v>
+      </c>
+      <c r="D48" t="s">
+        <v>180</v>
+      </c>
+      <c r="E48" t="s">
+        <v>408</v>
+      </c>
+      <c r="F48" t="s">
+        <v>409</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>411</v>
+      </c>
+      <c r="B49" t="s">
+        <v>412</v>
+      </c>
+      <c r="C49" t="s">
+        <v>413</v>
+      </c>
+      <c r="D49" t="s">
+        <v>180</v>
+      </c>
+      <c r="E49" t="s">
+        <v>414</v>
+      </c>
+      <c r="F49" t="s">
+        <v>415</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>417</v>
+      </c>
+      <c r="B50" t="s">
+        <v>418</v>
+      </c>
+      <c r="C50" t="s">
+        <v>237</v>
+      </c>
+      <c r="D50" t="s">
+        <v>180</v>
+      </c>
+      <c r="E50" t="s">
+        <v>419</v>
+      </c>
+      <c r="F50" t="s">
+        <v>420</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>422</v>
+      </c>
+      <c r="B51" t="s">
+        <v>423</v>
+      </c>
+      <c r="C51" t="s">
+        <v>237</v>
+      </c>
+      <c r="D51" t="s">
+        <v>180</v>
+      </c>
+      <c r="E51" t="s">
+        <v>424</v>
+      </c>
+      <c r="F51" t="s">
+        <v>425</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>427</v>
+      </c>
+      <c r="B52" t="s">
+        <v>428</v>
+      </c>
+      <c r="C52" t="s">
+        <v>237</v>
+      </c>
+      <c r="D52" t="s">
+        <v>180</v>
+      </c>
+      <c r="E52" t="s">
+        <v>429</v>
+      </c>
+      <c r="F52" t="s">
+        <v>430</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>432</v>
+      </c>
+      <c r="B53" t="s">
+        <v>433</v>
+      </c>
+      <c r="C53" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" t="s">
+        <v>180</v>
+      </c>
+      <c r="E53" t="s">
+        <v>434</v>
+      </c>
+      <c r="F53" t="s">
+        <v>435</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>437</v>
+      </c>
+      <c r="B54" t="s">
+        <v>166</v>
+      </c>
+      <c r="C54" t="s">
+        <v>167</v>
+      </c>
+      <c r="D54" t="s">
+        <v>168</v>
+      </c>
+      <c r="E54" t="s">
+        <v>438</v>
+      </c>
+      <c r="F54" t="s">
+        <v>163</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>440</v>
+      </c>
+      <c r="B55" t="s">
+        <v>441</v>
+      </c>
+      <c r="C55" t="s">
+        <v>442</v>
+      </c>
+      <c r="D55" t="s">
+        <v>180</v>
+      </c>
+      <c r="E55" t="s">
+        <v>443</v>
+      </c>
+      <c r="F55" t="s">
+        <v>444</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>446</v>
+      </c>
+      <c r="B56" t="s">
+        <v>363</v>
+      </c>
+      <c r="C56" t="s">
+        <v>447</v>
+      </c>
+      <c r="D56" t="s">
+        <v>180</v>
+      </c>
+      <c r="E56" t="s">
+        <v>448</v>
+      </c>
+      <c r="F56" t="s">
+        <v>366</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>450</v>
+      </c>
+      <c r="B57" t="s">
+        <v>451</v>
+      </c>
+      <c r="C57" t="s">
+        <v>452</v>
+      </c>
+      <c r="D57" t="s">
+        <v>180</v>
+      </c>
+      <c r="E57" t="s">
+        <v>453</v>
+      </c>
+      <c r="F57" t="s">
+        <v>454</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>456</v>
+      </c>
+      <c r="B58" t="s">
+        <v>457</v>
+      </c>
+      <c r="C58" t="s">
+        <v>458</v>
+      </c>
+      <c r="D58" t="s">
+        <v>180</v>
+      </c>
+      <c r="E58" t="s">
+        <v>459</v>
+      </c>
+      <c r="F58" t="s">
+        <v>162</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>461</v>
+      </c>
+      <c r="B59" t="s">
+        <v>462</v>
+      </c>
+      <c r="C59" t="s">
+        <v>463</v>
+      </c>
+      <c r="D59" t="s">
+        <v>180</v>
+      </c>
+      <c r="E59" t="s">
+        <v>464</v>
+      </c>
+      <c r="F59" t="s">
+        <v>162</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>466</v>
+      </c>
+      <c r="B60" t="s">
+        <v>467</v>
+      </c>
+      <c r="C60" t="s">
+        <v>237</v>
+      </c>
+      <c r="D60" t="s">
+        <v>180</v>
+      </c>
+      <c r="E60" t="s">
+        <v>468</v>
+      </c>
+      <c r="F60" t="s">
+        <v>469</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>471</v>
+      </c>
+      <c r="B61" t="s">
+        <v>418</v>
+      </c>
+      <c r="C61" t="s">
+        <v>237</v>
+      </c>
+      <c r="D61" t="s">
+        <v>180</v>
+      </c>
+      <c r="E61" t="s">
+        <v>419</v>
+      </c>
+      <c r="F61" t="s">
+        <v>420</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>473</v>
+      </c>
+      <c r="B62" t="s">
+        <v>474</v>
+      </c>
+      <c r="C62" t="s">
+        <v>475</v>
+      </c>
+      <c r="D62" t="s">
+        <v>476</v>
+      </c>
+      <c r="E62" t="s">
+        <v>477</v>
+      </c>
+      <c r="F62" t="s">
+        <v>478</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>480</v>
+      </c>
+      <c r="B63" t="s">
+        <v>391</v>
+      </c>
+      <c r="C63" t="s">
+        <v>481</v>
+      </c>
+      <c r="D63" t="s">
+        <v>180</v>
+      </c>
+      <c r="E63" t="s">
+        <v>482</v>
+      </c>
+      <c r="F63" t="s">
+        <v>393</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>484</v>
+      </c>
+      <c r="B64" t="s">
+        <v>485</v>
+      </c>
+      <c r="C64" t="s">
+        <v>486</v>
+      </c>
+      <c r="D64" t="s">
+        <v>180</v>
+      </c>
+      <c r="E64" t="s">
+        <v>487</v>
+      </c>
+      <c r="F64" t="s">
+        <v>488</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>490</v>
+      </c>
+      <c r="B65" t="s">
+        <v>491</v>
+      </c>
+      <c r="C65" t="s">
+        <v>402</v>
+      </c>
+      <c r="D65" t="s">
+        <v>180</v>
+      </c>
+      <c r="E65" t="s">
+        <v>492</v>
+      </c>
+      <c r="F65" t="s">
+        <v>493</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>495</v>
+      </c>
+      <c r="B66" t="s">
+        <v>496</v>
+      </c>
+      <c r="C66" t="s">
+        <v>334</v>
+      </c>
+      <c r="D66" t="s">
+        <v>180</v>
+      </c>
+      <c r="E66" t="s">
+        <v>497</v>
+      </c>
+      <c r="F66" t="s">
+        <v>498</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>500</v>
+      </c>
+      <c r="B67" t="s">
+        <v>501</v>
+      </c>
+      <c r="C67" t="s">
+        <v>502</v>
+      </c>
+      <c r="D67" t="s">
+        <v>180</v>
+      </c>
+      <c r="E67" t="s">
+        <v>503</v>
+      </c>
+      <c r="F67" t="s">
+        <v>504</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -562,7 +4717,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -601,8 +4756,898 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2" t="s">
+        <v>509</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F3" t="s">
+        <v>513</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>515</v>
+      </c>
+      <c r="B4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C4" t="s">
+        <v>517</v>
+      </c>
+      <c r="D4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" t="s">
+        <v>509</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>519</v>
+      </c>
+      <c r="B5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C5" t="s">
+        <v>521</v>
+      </c>
+      <c r="D5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F5" t="s">
+        <v>509</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>523</v>
+      </c>
+      <c r="B6" t="s">
+        <v>524</v>
+      </c>
+      <c r="C6" t="s">
+        <v>525</v>
+      </c>
+      <c r="D6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6" t="s">
+        <v>509</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>527</v>
+      </c>
+      <c r="B7" t="s">
+        <v>528</v>
+      </c>
+      <c r="C7" t="s">
+        <v>529</v>
+      </c>
+      <c r="D7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" t="s">
+        <v>509</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B8" t="s">
+        <v>532</v>
+      </c>
+      <c r="C8" t="s">
+        <v>533</v>
+      </c>
+      <c r="D8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" t="s">
+        <v>509</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>535</v>
+      </c>
+      <c r="B9" t="s">
+        <v>536</v>
+      </c>
+      <c r="C9" t="s">
+        <v>537</v>
+      </c>
+      <c r="D9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F9" t="s">
+        <v>509</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>539</v>
+      </c>
+      <c r="B10" t="s">
+        <v>540</v>
+      </c>
+      <c r="C10" t="s">
+        <v>541</v>
+      </c>
+      <c r="D10" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" t="s">
+        <v>162</v>
+      </c>
+      <c r="F10" t="s">
+        <v>509</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>543</v>
+      </c>
+      <c r="B11" t="s">
+        <v>544</v>
+      </c>
+      <c r="C11" t="s">
+        <v>545</v>
+      </c>
+      <c r="D11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E11" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11" t="s">
+        <v>509</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>547</v>
+      </c>
+      <c r="B12" t="s">
+        <v>548</v>
+      </c>
+      <c r="C12" t="s">
+        <v>549</v>
+      </c>
+      <c r="D12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F12" t="s">
+        <v>509</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>551</v>
+      </c>
+      <c r="B13" t="s">
+        <v>552</v>
+      </c>
+      <c r="C13" t="s">
+        <v>304</v>
+      </c>
+      <c r="D13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E13" t="s">
+        <v>162</v>
+      </c>
+      <c r="F13" t="s">
+        <v>509</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>554</v>
+      </c>
+      <c r="B14" t="s">
+        <v>555</v>
+      </c>
+      <c r="C14" t="s">
+        <v>556</v>
+      </c>
+      <c r="D14" t="s">
+        <v>162</v>
+      </c>
+      <c r="E14" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" t="s">
+        <v>513</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>558</v>
+      </c>
+      <c r="B15" t="s">
+        <v>559</v>
+      </c>
+      <c r="C15" t="s">
+        <v>560</v>
+      </c>
+      <c r="D15" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" t="s">
+        <v>561</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>563</v>
+      </c>
+      <c r="B16" t="s">
+        <v>564</v>
+      </c>
+      <c r="C16" t="s">
+        <v>565</v>
+      </c>
+      <c r="D16" t="s">
+        <v>162</v>
+      </c>
+      <c r="E16" t="s">
+        <v>162</v>
+      </c>
+      <c r="F16" t="s">
+        <v>566</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>568</v>
+      </c>
+      <c r="B17" t="s">
+        <v>569</v>
+      </c>
+      <c r="C17" t="s">
+        <v>242</v>
+      </c>
+      <c r="D17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" t="s">
+        <v>509</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>571</v>
+      </c>
+      <c r="B18" t="s">
+        <v>572</v>
+      </c>
+      <c r="C18" t="s">
+        <v>573</v>
+      </c>
+      <c r="D18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" t="s">
+        <v>162</v>
+      </c>
+      <c r="F18" t="s">
+        <v>509</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>575</v>
+      </c>
+      <c r="B19" t="s">
+        <v>576</v>
+      </c>
+      <c r="C19" t="s">
+        <v>577</v>
+      </c>
+      <c r="D19" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" t="s">
+        <v>513</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>579</v>
+      </c>
+      <c r="B20" t="s">
+        <v>580</v>
+      </c>
+      <c r="C20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D20" t="s">
+        <v>162</v>
+      </c>
+      <c r="E20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F20" t="s">
+        <v>509</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>583</v>
+      </c>
+      <c r="B21" t="s">
+        <v>584</v>
+      </c>
+      <c r="C21" t="s">
+        <v>585</v>
+      </c>
+      <c r="D21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E21" t="s">
+        <v>162</v>
+      </c>
+      <c r="F21" t="s">
+        <v>509</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>587</v>
+      </c>
+      <c r="B22" t="s">
+        <v>588</v>
+      </c>
+      <c r="C22" t="s">
+        <v>589</v>
+      </c>
+      <c r="D22" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" t="s">
+        <v>162</v>
+      </c>
+      <c r="F22" t="s">
+        <v>513</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>591</v>
+      </c>
+      <c r="B23" t="s">
+        <v>592</v>
+      </c>
+      <c r="C23" t="s">
+        <v>593</v>
+      </c>
+      <c r="D23" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" t="s">
+        <v>162</v>
+      </c>
+      <c r="F23" t="s">
+        <v>509</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>595</v>
+      </c>
+      <c r="B24" t="s">
+        <v>596</v>
+      </c>
+      <c r="C24" t="s">
+        <v>560</v>
+      </c>
+      <c r="D24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" t="s">
+        <v>162</v>
+      </c>
+      <c r="F24" t="s">
+        <v>509</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>598</v>
+      </c>
+      <c r="B25" t="s">
+        <v>599</v>
+      </c>
+      <c r="C25" t="s">
+        <v>600</v>
+      </c>
+      <c r="D25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25" t="s">
+        <v>162</v>
+      </c>
+      <c r="F25" t="s">
+        <v>509</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>602</v>
+      </c>
+      <c r="B26" t="s">
+        <v>548</v>
+      </c>
+      <c r="C26" t="s">
+        <v>549</v>
+      </c>
+      <c r="D26" t="s">
+        <v>162</v>
+      </c>
+      <c r="E26" t="s">
+        <v>162</v>
+      </c>
+      <c r="F26" t="s">
+        <v>513</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>604</v>
+      </c>
+      <c r="B27" t="s">
+        <v>507</v>
+      </c>
+      <c r="C27" t="s">
+        <v>605</v>
+      </c>
+      <c r="D27" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" t="s">
+        <v>162</v>
+      </c>
+      <c r="F27" t="s">
+        <v>509</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>607</v>
+      </c>
+      <c r="B28" t="s">
+        <v>608</v>
+      </c>
+      <c r="C28" t="s">
+        <v>541</v>
+      </c>
+      <c r="D28" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F28" t="s">
+        <v>509</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>610</v>
+      </c>
+      <c r="B29" t="s">
+        <v>611</v>
+      </c>
+      <c r="C29" t="s">
+        <v>612</v>
+      </c>
+      <c r="D29" t="s">
+        <v>162</v>
+      </c>
+      <c r="E29" t="s">
+        <v>162</v>
+      </c>
+      <c r="F29" t="s">
+        <v>613</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>615</v>
+      </c>
+      <c r="B30" t="s">
+        <v>608</v>
+      </c>
+      <c r="C30" t="s">
+        <v>541</v>
+      </c>
+      <c r="D30" t="s">
+        <v>162</v>
+      </c>
+      <c r="E30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F30" t="s">
+        <v>616</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>618</v>
+      </c>
+      <c r="B31" t="s">
+        <v>619</v>
+      </c>
+      <c r="C31" t="s">
+        <v>620</v>
+      </c>
+      <c r="D31" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" t="s">
+        <v>162</v>
+      </c>
+      <c r="F31" t="s">
+        <v>509</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>622</v>
+      </c>
+      <c r="B32" t="s">
+        <v>623</v>
+      </c>
+      <c r="C32" t="s">
+        <v>624</v>
+      </c>
+      <c r="D32" t="s">
+        <v>162</v>
+      </c>
+      <c r="E32" t="s">
+        <v>162</v>
+      </c>
+      <c r="F32" t="s">
+        <v>509</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>626</v>
+      </c>
+      <c r="B33" t="s">
+        <v>627</v>
+      </c>
+      <c r="C33" t="s">
+        <v>370</v>
+      </c>
+      <c r="D33" t="s">
+        <v>162</v>
+      </c>
+      <c r="E33" t="s">
+        <v>162</v>
+      </c>
+      <c r="F33" t="s">
+        <v>509</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>629</v>
+      </c>
+      <c r="B34" t="s">
+        <v>630</v>
+      </c>
+      <c r="C34" t="s">
+        <v>631</v>
+      </c>
+      <c r="D34" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" t="s">
+        <v>162</v>
+      </c>
+      <c r="F34" t="s">
+        <v>509</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>633</v>
+      </c>
+      <c r="B35" t="s">
+        <v>569</v>
+      </c>
+      <c r="C35" t="s">
+        <v>242</v>
+      </c>
+      <c r="D35" t="s">
+        <v>162</v>
+      </c>
+      <c r="E35" t="s">
+        <v>162</v>
+      </c>
+      <c r="F35" t="s">
+        <v>509</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>635</v>
+      </c>
+      <c r="B36" t="s">
+        <v>636</v>
+      </c>
+      <c r="C36" t="s">
+        <v>541</v>
+      </c>
+      <c r="D36" t="s">
+        <v>162</v>
+      </c>
+      <c r="E36" t="s">
+        <v>162</v>
+      </c>
+      <c r="F36" t="s">
+        <v>613</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>638</v>
+      </c>
+      <c r="B37" t="s">
+        <v>639</v>
+      </c>
+      <c r="C37" t="s">
+        <v>640</v>
+      </c>
+      <c r="D37" t="s">
+        <v>162</v>
+      </c>
+      <c r="E37" t="s">
+        <v>162</v>
+      </c>
+      <c r="F37" t="s">
+        <v>641</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>643</v>
+      </c>
+      <c r="B38" t="s">
+        <v>540</v>
+      </c>
+      <c r="C38" t="s">
+        <v>644</v>
+      </c>
+      <c r="D38" t="s">
+        <v>162</v>
+      </c>
+      <c r="E38" t="s">
+        <v>162</v>
+      </c>
+      <c r="F38" t="s">
+        <v>613</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-02.xlsx
+++ b/docs/xlsx/jobs-2026-09-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="948">
   <si>
     <t>Title</t>
   </si>
@@ -490,6 +490,27 @@
     <t>https://www.conservationjobboard.com/job-listing-southeast-region-lands-project-manager-washington-dc/7409963237</t>
   </si>
   <si>
+    <t>Regenerative Community Activist</t>
+  </si>
+  <si>
+    <t>Ernest Rodriguez/Farm Fresh To You</t>
+  </si>
+  <si>
+    <t>Berkeley, California, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Sustainable Agriculture / Food</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/regenerative-community-activist/</t>
+  </si>
+  <si>
     <t>🌍 Líder de Equipo F2F | Donantes Individuales | Turno Mañana o Tarde | CABA</t>
   </si>
   <si>
@@ -502,9 +523,6 @@
     <t>Contract</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Children Youth, Community Development, Education</t>
   </si>
   <si>
@@ -568,6 +586,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/e5a837b9c63f4932ac0bb37757d9ca7c-adolescent-representation-unit-attorney-brooklyn-defender-services-brooklyn</t>
   </si>
   <si>
+    <t>Advocacy &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>Katal Center for Equity, Health, and Justice</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ccee2454085c40d5a2e15f54e4feb036-advocacy-communications-manager-katal-center-for-equity-health-and-justice-kings-county</t>
+  </si>
+  <si>
     <t>Annual Giving Manager (New York)</t>
   </si>
   <si>
@@ -634,6 +670,75 @@
     <t>https://www.idealist.org/en/government-job/fbd4216211204daf85caaafd33de57ab-assistant-attorney-general-office-of-the-massachusetts-attorney-general-springfield</t>
   </si>
   <si>
+    <t>Assistant Director, Media</t>
+  </si>
+  <si>
+    <t>The Institute for Health Metrics and Evaluation</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 130008.00 - 162000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c06d87fb741b4b97ba104a6b08a1a615-assistant-director-media-the-institute-for-health-metrics-and-evaluation-seattle</t>
+  </si>
+  <si>
+    <t>Associate Director of Community Engagements &amp; Partnerships</t>
+  </si>
+  <si>
+    <t>Washington State Opportunity Scholarship</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 112662.00 - 112662.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f51f84d8f9f4408be519dca6682f95e-associate-director-of-community-engagements-partnerships-washington-state-opportunity-scholarship-seattle</t>
+  </si>
+  <si>
+    <t>Associate Director of Policy and Advocacy</t>
+  </si>
+  <si>
+    <t>UnCommon Law</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 99000.00 - 118250.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Legal Assistance, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b385500924e4e26be6e7ddf335685dd-associate-director-of-policy-and-advocacy-uncommon-law-oakland</t>
+  </si>
+  <si>
+    <t>Associate Strategic Campaign Director</t>
+  </si>
+  <si>
+    <t>Council on American-Islamic Relations - National Headquarters</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d2bfcdf0f004258b947a8bb06fffc68-associate-strategic-campaign-director-council-on-american-islamic-relations-national-headquarters-washington</t>
+  </si>
+  <si>
     <t>Bilingual Front Desk Receptionist (English/Spanish)</t>
   </si>
   <si>
@@ -688,6 +793,87 @@
     <t>https://www.idealist.org/en/nonprofit-job/41782f919a944e458281220fb5c41fe4-captadores-de-socios-y-lider-de-equipo-para-via-publica-en-el-departamento-de-salto-uruguay-medicos-sin-fronteras-lat-salto</t>
   </si>
   <si>
+    <t>Case Manager (Multiple Openings)</t>
+  </si>
+  <si>
+    <t>Amirah, Inc.</t>
+  </si>
+  <si>
+    <t>Beverly, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 59000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Mental Health, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96feeec3ae2e4f4ca9677b6e5d3d2148-case-manager-multiple-openings-amirah-inc-beverly</t>
+  </si>
+  <si>
+    <t>Case Manager (Stay Housed LA) - Eviction Defense Center Workgroup</t>
+  </si>
+  <si>
+    <t>Legal Aid Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 54080.00 - 71165.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b60134e6de2d4d5397f3bc34daea4a16-case-manager-stay-housed-la-eviction-defense-center-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer (CEO)</t>
+  </si>
+  <si>
+    <t>VisionGift</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8dfd48fbd36d47cb89abda98ec869b57-chief-executive-officer-ceo-visiongift-portland</t>
+  </si>
+  <si>
+    <t>Clinical Program Manager</t>
+  </si>
+  <si>
+    <t>Partnerships for Trauma Recovery</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca829547b9e1471ba132a4a8c061be34-clinical-program-manager-partnerships-for-trauma-recovery-berkeley</t>
+  </si>
+  <si>
+    <t>College &amp; Career Readiness Coach (INSPIRES)</t>
+  </si>
+  <si>
+    <t>The Bronx Institute at Lehman College - CUNY</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c18378c19c9b4b5bb132524ab62de83b-college-career-readiness-coach-inspires-the-bronx-institute-at-lehman-college-cuny-bronx-county</t>
+  </si>
+  <si>
     <t>College and Career Advisor</t>
   </si>
   <si>
@@ -721,15 +907,105 @@
     <t>https://www.idealist.org/en/nonprofit-job/ca2bd12aa28b4e45a02dbfd1bbb80b32-communications-and-design-coordinator-detroit-disability-power-detroit</t>
   </si>
   <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>MAZON: A Jewish Response to Hunger</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 64000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6418731f6363458e9cc605e903e6f012-communications-associate-mazon-a-jewish-response-to-hunger-washington</t>
+  </si>
+  <si>
+    <t>Community Outreach Representative</t>
+  </si>
+  <si>
+    <t>Rosales Communications</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Communications Access, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/677d2ea4fcb04825a23392fdace5e8fb-community-outreach-representative-rosales-communications-philadelphia</t>
+  </si>
+  <si>
+    <t>Conscious Kitchen | Program Coordinator</t>
+  </si>
+  <si>
+    <t>Turning Green</t>
+  </si>
+  <si>
+    <t>Sausalito, California</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/682229b23b1a40f5b30d983884d5506b-conscious-kitchen-program-coordinator-turning-green-sausalito</t>
+  </si>
+  <si>
+    <t>Conscious Kitchen | Senior Program &amp; Grants Manager</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc3b6f845fef4df58aba6ab260ac98d4-conscious-kitchen-senior-program-grants-manager-turning-green-sausalito</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>National Parks Conservation Association</t>
+  </si>
+  <si>
+    <t>USD 116000.00 - 139000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27b576d2122d46c681876f69e665133f-controller-national-parks-conservation-association-washington</t>
+  </si>
+  <si>
+    <t>Deputy Director, Procurement &amp; Operations</t>
+  </si>
+  <si>
+    <t>NYC Kids RISE</t>
+  </si>
+  <si>
+    <t>Long Island City, New York</t>
+  </si>
+  <si>
+    <t>USD 91200.00 - 114000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f6724e90cc94d70b6d633cf9dc54ce1-deputy-director-procurement-operations-nyc-kids-rise-long-island-city</t>
+  </si>
+  <si>
     <t>Development and Partnership Manager</t>
   </si>
   <si>
     <t>Not One More Vet, Inc.</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>Health Medicine, Job Workplace, Mental Health</t>
   </si>
   <si>
@@ -787,6 +1063,75 @@
     <t>https://www.idealist.org/en/nonprofit-job/3440dd4dbdf444839986a579902816ca-development-manager-aisling-irish-community-center-inc-yonkers</t>
   </si>
   <si>
+    <t>Westchester Residential Opportunities, Inc.</t>
+  </si>
+  <si>
+    <t>White Plains, New York</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2496af4a6aa84e009d6bf89d27869200-development-manager-westchester-residential-opportunities-inc-white-plains</t>
+  </si>
+  <si>
+    <t>Governors Action Alliance (GovAct)</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Reproductive Health Rights, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/3bbba48e815c4140b333616e8f5c10ed-development-manager-governors-action-alliance-govact-washington</t>
+  </si>
+  <si>
+    <t>Development Operations Administrator</t>
+  </si>
+  <si>
+    <t>Bread for the World, Inc.</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Poverty, Hunger Food Security, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc3ae6b34803404796306f809cd6fa43-development-operations-administrator-bread-for-the-world-inc-washington</t>
+  </si>
+  <si>
+    <t>Digital Marketing Lead</t>
+  </si>
+  <si>
+    <t>SaverLife</t>
+  </si>
+  <si>
+    <t>USD 72880.00 - 91100.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Consumer Protection, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7dd0c0a5bdac44ad81b703767eed41ae-digital-marketing-lead-saverlife-san-francisco</t>
+  </si>
+  <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>Essential Access Health</t>
+  </si>
+  <si>
+    <t>USD 132094.00 - 132094.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f488cf6c37c4eaea925c58390895776-director-of-communications-essential-access-health-los-angeles</t>
+  </si>
+  <si>
     <t>Director of Development</t>
   </si>
   <si>
@@ -805,6 +1150,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/7ee9090a56ae42af8d1fca177be71ab4-director-of-development-womens-money-matters-boston</t>
   </si>
   <si>
+    <t>Uptown People's Law Center</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Disability, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c1b1891dc2a74be188f75d2948963f33-director-of-development-uptown-peoples-law-center-chicago</t>
+  </si>
+  <si>
+    <t>Academy for Local Leadership</t>
+  </si>
+  <si>
+    <t>Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/677a80b4f10c4238a8f43475fb1b8b5b-director-of-development-academy-for-local-leadership-chicago</t>
+  </si>
+  <si>
+    <t>Director of Development (Major Gifts &amp; Fundraising Leadership)</t>
+  </si>
+  <si>
+    <t>Habitat for Humanity of Long Island</t>
+  </si>
+  <si>
+    <t>Ronkonkoma, New York</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aac7585ef11340f78a0c3ae30c14df56-director-of-development-major-gifts-fundraising-leadership-habitat-for-humanity-of-long-island-ronkonkoma</t>
+  </si>
+  <si>
     <t>Director of Development and Communications</t>
   </si>
   <si>
@@ -835,15 +1219,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/bd2a1cc7b1404f4192cb31b504616682-director-of-finance-and-operations-institute-for-contemporary-psychotherapy-new-york</t>
   </si>
   <si>
+    <t>Director of Jacj Cuisi Wildlife Sanctuary</t>
+  </si>
+  <si>
+    <t>San Buena Ventura, La Paz, Bolivia, Departamento de La Paz, BO</t>
+  </si>
+  <si>
+    <t>USD 400.00 - 450.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b9a1185b9cac4e7dbe425c873e949ad8-director-of-jacj-cuisi-wildlife-sanctuary-comunidad-inti-wara-yassi-ciwy-san-buena-ventura-la-paz-bolivia</t>
+  </si>
+  <si>
     <t>Director of Programs</t>
   </si>
   <si>
     <t>Girls Inc. of Los Angeles</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 86000.00 - 90000.00/year</t>
   </si>
   <si>
@@ -853,18 +1246,66 @@
     <t>Director of State Policy</t>
   </si>
   <si>
-    <t>MAZON: A Jewish Response to Hunger</t>
-  </si>
-  <si>
     <t>USD 110000.00 - 119000.00/year</t>
   </si>
   <si>
-    <t>Hunger Food Security, Policy</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/e52e3aa99fc04e88bf7e9019889f0906-director-of-state-policy-mazon-a-jewish-response-to-hunger-los-angeles</t>
   </si>
   <si>
+    <t>Director, 3DE - Prince George's County</t>
+  </si>
+  <si>
+    <t>Junior Achievement of Greater Washington</t>
+  </si>
+  <si>
+    <t>Prince George's County, Maryland</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b826aa33509743928d6cb93a4139e45e-director-3de-prince-georges-county-junior-achievement-of-greater-washington-prince-georges-county</t>
+  </si>
+  <si>
+    <t>Director, People Operations &amp; Talent</t>
+  </si>
+  <si>
+    <t>Carlos Rosario</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/b7447523105145c591f7e8f988895e9d-director-people-operations-talent-carlos-rosario-washington</t>
+  </si>
+  <si>
+    <t>Director/a del Santuario Jacj Cuisi</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbb610d106b54f5dbd62e940a998c5ac-directora-del-santuario-jacj-cuisi-comunidad-inti-wara-yassi-ciwy-san-buena-ventura-la-paz-bolivia</t>
+  </si>
+  <si>
+    <t>Donor Operations Coordinator</t>
+  </si>
+  <si>
+    <t>The Good Food Institute</t>
+  </si>
+  <si>
+    <t>USD 36466.00 - 37669.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61a1bef6f7084768bbe3f80acf52df75-donor-operations-coordinator-the-good-food-institute-arlington</t>
+  </si>
+  <si>
     <t>Donor Relations Manager</t>
   </si>
   <si>
@@ -895,15 +1336,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/900c9814a94f4d2e834647eb5e02b1b4-education-debt-legal-manager-cssny-new-york</t>
   </si>
   <si>
+    <t>Employment Consultant</t>
+  </si>
+  <si>
+    <t>Supported Solution</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/43fcf58f300e450a887bcda1849e0b48-employment-consultant-supported-solution-seattle</t>
+  </si>
+  <si>
+    <t>Environmental Analyst</t>
+  </si>
+  <si>
+    <t>NEIWPCC</t>
+  </si>
+  <si>
+    <t>Grand Isle, Vermont</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Science Technology, Water Sanitation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b89f84d98d1842dead8c3a095b3a0028-environmental-analyst-neiwpcc-grand-isle</t>
+  </si>
+  <si>
+    <t>Environmental Analyst – Lead Testing in Schools</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ecddaf7a71c143eab06eb76c213776e8-environmental-analyst-lead-testing-in-schools-neiwpcc-providence</t>
+  </si>
+  <si>
     <t>Events and Special Projects Assistant</t>
   </si>
   <si>
     <t>Center for US Global Leadership</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 42000.00 - 45000.00/year</t>
   </si>
   <si>
@@ -913,6 +1396,75 @@
     <t>https://www.idealist.org/en/nonprofit-job/a98cef008a4a425a9df4edc6aae405b1-events-and-special-projects-assistant-center-for-us-global-leadership-washington</t>
   </si>
   <si>
+    <t>Executive &amp; Operations Assistant</t>
+  </si>
+  <si>
+    <t>Community Inclusion &amp; Development Alliance Inc</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 62500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d0c4c14143940db859b1d08a636b567-executive-operations-assistant-community-inclusion-development-alliance-inc-queens-county</t>
+  </si>
+  <si>
+    <t>Kenai Watershed Forum</t>
+  </si>
+  <si>
+    <t>Soldotna, Alaska</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Science Technology, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ec9a1d4cc3d44709a83d627279a0989-executive-director-kenai-watershed-forum-soldotna</t>
+  </si>
+  <si>
+    <t>Habitat for Humanity Capital District</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9363e696647540468933bbe25d306951-executive-director-habitat-for-humanity-capital-district-albany</t>
+  </si>
+  <si>
+    <t>Executive Director, Women for Sobriety</t>
+  </si>
+  <si>
+    <t>WOMEN FOR SOBRIETY INC</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Substance Abuse Addiction, Women, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b0bd4970d2a4043af9084182786ca55-executive-director-women-for-sobriety-women-for-sobriety-inc-quakertown</t>
+  </si>
+  <si>
+    <t>Fee-for-Service Nurse</t>
+  </si>
+  <si>
+    <t>Concerned Home Managers for the Elderly, Inc.</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2d68f78d230424a9e7fbe68978343f5-fee-for-service-nurse-concerned-home-managers-for-the-elderly-inc-new-york</t>
+  </si>
+  <si>
     <t>Financial Aid Specialist - Part-time</t>
   </si>
   <si>
@@ -940,6 +1492,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/b52ca8eaa9294157880fbc991a77b98e-food-pantry-coordinator-a-place-to-turn-natick</t>
   </si>
   <si>
+    <t>Founders Lab Instructor (Part-Time, Fall 2026)</t>
+  </si>
+  <si>
+    <t>Urban Arts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c32aae5e9cc4d2c9bc6b98538bec4c8-founders-lab-instructor-part-time-fall-2026-urban-arts-new-york</t>
+  </si>
+  <si>
     <t>Get Out The Vote Kansas Phone Banker</t>
   </si>
   <si>
@@ -991,9 +1552,6 @@
     <t>CaringKind, The Heart of Alzheimer’s Caregiving</t>
   </si>
   <si>
-    <t>USD 60000.00 - 65000.00/year</t>
-  </si>
-  <si>
     <t>Education, Mental Health, Seniors Retirement</t>
   </si>
   <si>
@@ -1012,6 +1570,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/b30f3bb1232a4c43a621013b267263b1-health-attorney-cssny-new-york</t>
   </si>
   <si>
+    <t>Heartland Fund Finance Manager</t>
+  </si>
+  <si>
+    <t>Clover Search Works</t>
+  </si>
+  <si>
+    <t>USD 79900.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/ef941cff4d024c35abeb2b685c0deeaa-heartland-fund-finance-manager-clover-search-works-baltimore</t>
+  </si>
+  <si>
+    <t>Heartland Fund Senior Operations Associate</t>
+  </si>
+  <si>
+    <t>USD 75650.00 - 89000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/a5f61aaaaa6a486ba374ae45f44deaa8-heartland-fund-senior-operations-associate-clover-search-works-baltimore</t>
+  </si>
+  <si>
     <t>Housing and Human Services Policy Analyst</t>
   </si>
   <si>
@@ -1039,9 +1618,6 @@
     <t>USD 65000.00 - 75000.00/year</t>
   </si>
   <si>
-    <t>Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/9958180699fd43c5ae06439a9d8992e2-hr-office-coordinator-paintcare-american-coatings-association-washington</t>
   </si>
   <si>
@@ -1060,6 +1636,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/75ba1d4bc186431aa5e6efc86c287663-human-resources-generalist-ecotarium-worcester</t>
   </si>
   <si>
+    <t>Human Resources Security, Clearance and Compliance Specialist</t>
+  </si>
+  <si>
+    <t>Brooklyn Community Services (BCS)</t>
+  </si>
+  <si>
+    <t>USD 66300.00 - 66301.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c46cd7b4b7145ecad46e794777a72d5-human-resources-security-clearance-and-compliance-specialist-brooklyn-community-services-bcs-kings-county</t>
+  </si>
+  <si>
     <t>Immigrant Rights and Worker Justice Organizer</t>
   </si>
   <si>
@@ -1078,6 +1669,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/a72c1ab3f56c4a7cb54433ab10f3de45-immigrant-rights-and-worker-justice-organizer-escucha-mi-voz-iowa-iowa-city</t>
   </si>
   <si>
+    <t>Impact Modeling Analyst</t>
+  </si>
+  <si>
+    <t>GitLab Foundation</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Entrepreneurship, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2949594a498a4586a49cf1c46580f5f8-impact-modeling-analyst-gitlab-foundation-san-francisco</t>
+  </si>
+  <si>
     <t>In-Home Counselor/Social Worker (serving Baxter, Boone, and Marion counties)</t>
   </si>
   <si>
@@ -1102,6 +1708,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/a60259835afd4d72b6ebb85eb3d9b3bf-in-home-counselorsocial-worker-serving-baxter-boone-and-marion-counties-youth-villages-mountain-home</t>
   </si>
   <si>
+    <t>Inclusion Coordinator</t>
+  </si>
+  <si>
+    <t>Temple Rodef Shalom</t>
+  </si>
+  <si>
+    <t>Falls Church, Virginia</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbd59be9da174ec29d07a0d39f2aea75-inclusion-coordinator-temple-rodef-shalom-falls-church</t>
+  </si>
+  <si>
+    <t>Individual Giving Coordinator</t>
+  </si>
+  <si>
+    <t>Hesperian Health Guides</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca19cd93427b46db86f71f81f27b4059-individual-giving-coordinator-hesperian-health-guides-oakland</t>
+  </si>
+  <si>
+    <t>Individual Giving Officer</t>
+  </si>
+  <si>
+    <t>Asian Law Caucus</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 143147.00 - 170925.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2efa88349d07457fb36e3c9ccb4c363c-individual-giving-officer-asian-law-caucus-san-francisco</t>
+  </si>
+  <si>
     <t>Junior Accountant</t>
   </si>
   <si>
@@ -1126,9 +1783,6 @@
     <t>Teamsters Local Union No. 705</t>
   </si>
   <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 100000.00/year</t>
   </si>
   <si>
@@ -1141,21 +1795,48 @@
     <t>Legal Services Director</t>
   </si>
   <si>
-    <t>Asian Law Caucus</t>
-  </si>
-  <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
     <t>USD 139050.00 - 176144.00/year</t>
   </si>
   <si>
-    <t>Housing Homelessness, Human Rights Civil Liberties, Immigrants Or Refugees</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/e3cb71fdba824106a9fc266ee2d91b3f-legal-services-director-asian-law-caucus-san-francisco</t>
   </si>
   <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>Type Media Center</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf744f411ef94d828e8f83dc3fd4bdbd-major-gifts-officer-type-media-center-new-york</t>
+  </si>
+  <si>
+    <t>Manager for Development Operations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac6435ad0c8346198523dbd228493326-manager-for-development-operations-bread-for-the-world-inc-washington</t>
+  </si>
+  <si>
+    <t>Manager of External Affairs, Advocacy and Campaigns</t>
+  </si>
+  <si>
+    <t>Rochester Education and Development for Youth (READY)</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a309d56de34f4d8ca7d5e2600cb1ac87-manager-of-external-affairs-advocacy-and-campaigns-rochester-education-and-development-for-youth-ready-rochester</t>
+  </si>
+  <si>
     <t>Manager, Summer Math Enrichment (Hyrbid - Los Angeles)</t>
   </si>
   <si>
@@ -1186,21 +1867,114 @@
     <t>https://www.idealist.org/en/nonprofit-job/d664db3b1c41404fbbfad85f90dd10ce-managing-attorney-church-world-service-new-york-dallas</t>
   </si>
   <si>
+    <t>Meeting and Education Specialist</t>
+  </si>
+  <si>
+    <t>Northwest Regional Primary Care Association</t>
+  </si>
+  <si>
+    <t>USD 29.82 - 34.25/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d56e807e2dcb45fba7bb59c3c597d0c2-meeting-and-education-specialist-northwest-regional-primary-care-association-seattle</t>
+  </si>
+  <si>
+    <t>Membership Experience Design Specialist</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 34.00 - 42.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/6dee1ff959ef4447b8c410376ec7feda-membership-experience-design-specialist-the-choice-inc-washington</t>
+  </si>
+  <si>
     <t>Network Development &amp; National Initiatives Director</t>
   </si>
   <si>
-    <t>Council on American-Islamic Relations - National Headquarters</t>
-  </si>
-  <si>
     <t>USD 95000.00 - 116000.00/year</t>
   </si>
   <si>
-    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d74350a358e34db6a31e68a5b5c35d12-network-development-national-initiatives-director-council-on-american-islamic-relations-national-headquarters-washington</t>
   </si>
   <si>
+    <t>Nourish Intake Associate (English/Spanish)</t>
+  </si>
+  <si>
+    <t>New York Common Pantry</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 21.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6d9004837ed46e98a2a52270345801e-nourish-intake-associate-englishspanish-new-york-common-pantry-bronx</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Rights CoLab</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1cad642657614d2fb7bd19189296c640-operations-manager-rights-colab-new-york</t>
+  </si>
+  <si>
+    <t>WildCare</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 77000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dbb2c00760fe42cd87e30346cc5483ab-operations-manager-wildcare-san-rafael</t>
+  </si>
+  <si>
+    <t>Organizing Apprenticeship - UNITE HERE Local 217</t>
+  </si>
+  <si>
+    <t>UNITE HERE!</t>
+  </si>
+  <si>
+    <t>Hartford, Connecticut</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05e2503800cb4cf79deab20085990373-organizing-apprenticeship-unite-here-local-217-unite-here-hartford</t>
+  </si>
+  <si>
+    <t>New London, Connecticut</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7a065dd2c524f6f93ae01c0a07fd747-organizing-apprenticeship-unite-here-local-217-unite-here-new-london</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/939a4c208fe54ec8a6026c83c537ba95-organizing-apprenticeship-unite-here-local-217-unite-here-new-haven</t>
+  </si>
+  <si>
     <t>Outreach Director – Western Region</t>
   </si>
   <si>
@@ -1222,9 +1996,6 @@
     <t>RiseBoro Community Partnership</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
     <t>USD 30.22 - 35.72/hour</t>
   </si>
   <si>
@@ -1234,6 +2005,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/c2c8f0ad07e240a78629187b22cb9780-paralegal-leap-riseboro-community-partnership-kings-county</t>
   </si>
   <si>
+    <t>Part-Time Food Rescue Driver</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3393266ca9f243f7ac9bea39b3288789-part-time-food-rescue-driver-new-york-common-pantry-new-york</t>
+  </si>
+  <si>
+    <t>Part-Time Help 365 Case Manager (English/Mandarin/Cantonese)</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bfa252c5ca3a4070b8be3d5d15149a2f-part-time-help-365-case-manager-englishmandarincantonese-new-york-common-pantry-new-york</t>
+  </si>
+  <si>
     <t>Payroll &amp; Benefits Specialist</t>
   </si>
   <si>
@@ -1282,6 +2071,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/4fe940538899432aad8993707aeaca23-policy-research-specialist-freefrom-los-angeles</t>
   </si>
   <si>
+    <t>Profesional en Biología - Trabaja con Fauna Silvestre Rescatada en la Selva Boliviana</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c565774904804599ab173e28df837cd3-profesional-en-biologia-trabaja-con-fauna-silvestre-rescatada-en-la-selva-boliviana-comunidad-inti-wara-yassi-ciwy-ascension-de-guarayos</t>
+  </si>
+  <si>
     <t>Program Assistant</t>
   </si>
   <si>
@@ -1327,6 +2122,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/5a42ec8bd7e44ccb8456826653331204-program-associate-restorative-justice-new-york-peace-institute-new-york</t>
   </si>
   <si>
+    <t>Program Instructor</t>
+  </si>
+  <si>
+    <t>Wildwoods, a project of Community Partners</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b41e477cc6194d5b943753ef2a5aac8b-program-instructor-wildwoods-a-project-of-community-partners-los-angeles</t>
+  </si>
+  <si>
     <t>Program Mentor ( Part-Time)</t>
   </si>
   <si>
@@ -1342,9 +2149,6 @@
     <t>AHSHAY</t>
   </si>
   <si>
-    <t>Seattle, Washington</t>
-  </si>
-  <si>
     <t>USD 81000.00 - 86000.00/year</t>
   </si>
   <si>
@@ -1354,6 +2158,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/c249fa010f414ed88e8710770df4d4ab-project-coordinator-ahshay-seattle</t>
   </si>
   <si>
+    <t>PT Bilingual Help 365 Bronx Case Manager (English/Spanish)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c747dc05bae497cbbcfed956d759fbd-pt-bilingual-help-365-bronx-case-manager-englishspanish-new-york-common-pantry-bronx</t>
+  </si>
+  <si>
+    <t>Research Assistant, Asia Program</t>
+  </si>
+  <si>
+    <t>Carnegie Endowment for International Peace</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a991e60f7944690964065eee09b4d87-research-assistant-asia-program-carnegie-endowment-for-international-peace-washington</t>
+  </si>
+  <si>
     <t>Resident Services Coordinator - The Exchange</t>
   </si>
   <si>
@@ -1399,15 +2224,54 @@
     <t>https://www.idealist.org/en/job/c222a9e9d7e14708ab709cde7620b97c-senior-manager-of-major-gifts-girl-scouts-of-connecticut-inc-north-haven</t>
   </si>
   <si>
+    <t>Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>California Center for Movement Legal Services</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/393bae419de44347ae9262044e7bea16-senior-staff-attorney-california-center-for-movement-legal-services-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior State Policy Associate</t>
+  </si>
+  <si>
+    <t>American Flood Coalition</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 99000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disaster Relief, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4f22ff305074e258b93350a26b3a480-senior-state-policy-associate-american-flood-coalition-washington</t>
+  </si>
+  <si>
+    <t>Special Education Compliance Manager</t>
+  </si>
+  <si>
+    <t>Mundo Verde Bilingual Public Charter School</t>
+  </si>
+  <si>
+    <t>USD 80945.00 - 93086.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb9f0fcb07b3463d8aeefa8bd2d4447d-special-education-compliance-manager-mundo-verde-bilingual-public-charter-school-washington</t>
+  </si>
+  <si>
     <t>Special Litigation Counsel: Albany Litigation Bureau (3908)</t>
   </si>
   <si>
     <t>New York State Office of the Attorney General</t>
   </si>
   <si>
-    <t>Albany, New York</t>
-  </si>
-  <si>
     <t>USD 87356.00 - 186493.00/year</t>
   </si>
   <si>
@@ -1429,6 +2293,30 @@
     <t>https://www.idealist.org/en/business-job/629b2395e97741dfb1d2f6b08ac59a2a-staff-attorney-sanctuary-of-the-south-chattanooga</t>
   </si>
   <si>
+    <t>USD 78000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b2b9fc8ad5d4e8caef20611e508d913-staff-attorney-california-center-for-movement-legal-services-los-angeles</t>
+  </si>
+  <si>
+    <t>Staff Attorney/Senior Staff Attorney – National Litigation</t>
+  </si>
+  <si>
+    <t>The Reporters Committee for Freedom of the Press</t>
+  </si>
+  <si>
+    <t>USD 128800.00 - 153100.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Media, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/36f00d5a9e7546db86b2c03ba5be0f2f-staff-attorneysenior-staff-attorney-national-litigation-the-reporters-committee-for-freedom-of-the-press-washington</t>
+  </si>
+  <si>
     <t>State Policy &amp; Advocacy Specialist</t>
   </si>
   <si>
@@ -1444,9 +2332,6 @@
     <t>Remote (California)</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 25.00 - 25.00/hour</t>
   </si>
   <si>
@@ -1456,12 +2341,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/96e0e52c710c48c1b1bbb5c84095de64-stop-data-centers-organizing-fellow-food-water-watch-bakersfield</t>
   </si>
   <si>
+    <t>Student Advisor</t>
+  </si>
+  <si>
+    <t>East Side House Settlement</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/51cd969905604cb0b6fc9f9151b7d87e-student-advisor-east-side-house-settlement-bronx-county</t>
+  </si>
+  <si>
+    <t>Systems &amp; Enablement Manager (monday.com)</t>
+  </si>
+  <si>
+    <t>Literations</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3091fe92cf374a55950dc722712d6c79-systems-enablement-manager-mondaycom-literations-boston</t>
+  </si>
+  <si>
     <t>Trial Attorney</t>
   </si>
   <si>
-    <t>Remote (Washington, District of Columbia)</t>
-  </si>
-  <si>
     <t>USD 95000.00 - 100000.00/year</t>
   </si>
   <si>
@@ -1874,9 +2783,6 @@
   </si>
   <si>
     <t>Riverdale Neighborhood House</t>
-  </si>
-  <si>
-    <t>Bronx, New York</t>
   </si>
   <si>
     <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72857763</t>
@@ -3035,7 +3941,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3074,8 +3980,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3083,7 +4015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3124,761 +4056,761 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E2" t="s">
         <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" t="s">
         <v>169</v>
       </c>
-      <c r="F3" t="s">
-        <v>163</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F4" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F5" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="D6" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E6" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F6" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D7" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E7" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F7" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D8" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="E8" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F8" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D9" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F9" t="s">
-        <v>162</v>
+        <v>211</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C10" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D10" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E10" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F10" t="s">
-        <v>210</v>
+        <v>162</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B11" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C11" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E11" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F11" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B12" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D12" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="E12" t="s">
-        <v>162</v>
+        <v>227</v>
       </c>
       <c r="F12" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B13" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C13" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="D13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E13" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F13" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B14" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C14" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D14" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E14" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F14" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B15" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C15" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E15" t="s">
-        <v>162</v>
+        <v>244</v>
       </c>
       <c r="F15" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B16" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C16" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D16" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E16" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F16" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B17" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="D17" t="s">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="E17" t="s">
-        <v>249</v>
+        <v>162</v>
       </c>
       <c r="F17" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B18" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C18" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E18" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="F18" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B19" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E19" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F19" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B20" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C20" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="D20" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E20" t="s">
-        <v>266</v>
+        <v>162</v>
       </c>
       <c r="F20" t="s">
-        <v>244</v>
+        <v>162</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B21" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C21" t="s">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="D21" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E21" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F21" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B22" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C22" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D22" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E22" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F22" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B23" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C23" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="D23" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E23" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="F23" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B24" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C24" t="s">
-        <v>173</v>
+        <v>293</v>
       </c>
       <c r="D24" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E24" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F24" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B25" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C25" t="s">
-        <v>173</v>
+        <v>299</v>
       </c>
       <c r="D25" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E25" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="F25" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B26" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C26" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="D26" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E26" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="F26" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>310</v>
       </c>
       <c r="C27" t="s">
-        <v>167</v>
+        <v>311</v>
       </c>
       <c r="D27" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="E27" t="s">
-        <v>300</v>
+        <v>162</v>
       </c>
       <c r="F27" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C28" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="D28" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E28" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="F28" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B29" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C29" t="s">
-        <v>237</v>
+        <v>299</v>
       </c>
       <c r="D29" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="E29" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="F29" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B30" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="C30" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="D30" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E30" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="F30" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B31" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C31" t="s">
-        <v>319</v>
+        <v>220</v>
       </c>
       <c r="D31" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E31" t="s">
-        <v>320</v>
+        <v>162</v>
       </c>
       <c r="F31" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B32" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C32" t="s">
-        <v>173</v>
+        <v>334</v>
       </c>
       <c r="D32" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E32" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="F32" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B33" t="s">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="C33" t="s">
-        <v>173</v>
+        <v>340</v>
       </c>
       <c r="D33" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E33" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F33" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C34" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="D34" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E34" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="F34" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -3886,456 +4818,456 @@
         <v>338</v>
       </c>
       <c r="B35" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C35" t="s">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="D35" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E35" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="F35" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C36" t="s">
-        <v>345</v>
+        <v>299</v>
       </c>
       <c r="D36" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E36" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="F36" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="C37" t="s">
-        <v>350</v>
+        <v>299</v>
       </c>
       <c r="D37" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E37" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F37" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C38" t="s">
-        <v>356</v>
+        <v>220</v>
       </c>
       <c r="D38" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F38" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="C39" t="s">
-        <v>360</v>
+        <v>267</v>
       </c>
       <c r="D39" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E39" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F39" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C40" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="D40" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E40" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="F40" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C41" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="D41" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E41" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="F41" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s">
+        <v>382</v>
+      </c>
+      <c r="C42" t="s">
+        <v>379</v>
+      </c>
+      <c r="D42" t="s">
+        <v>186</v>
+      </c>
+      <c r="E42" t="s">
         <v>375</v>
       </c>
-      <c r="C42" t="s">
-        <v>376</v>
-      </c>
-      <c r="D42" t="s">
-        <v>180</v>
-      </c>
-      <c r="E42" t="s">
-        <v>377</v>
-      </c>
       <c r="F42" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C43" t="s">
-        <v>275</v>
+        <v>387</v>
       </c>
       <c r="D43" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E43" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="F43" t="s">
-        <v>187</v>
+        <v>389</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C44" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="D44" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E44" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="F44" t="s">
-        <v>388</v>
+        <v>336</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B45" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C45" t="s">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="D45" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E45" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F45" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B46" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="C46" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D46" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E46" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="F46" t="s">
-        <v>398</v>
+        <v>251</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C47" t="s">
-        <v>402</v>
+        <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E47" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F47" t="s">
-        <v>404</v>
+        <v>169</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s">
-        <v>407</v>
+        <v>298</v>
       </c>
       <c r="C48" t="s">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E48" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F48" t="s">
-        <v>409</v>
+        <v>301</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B49" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D49" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E49" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F49" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B50" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C50" t="s">
-        <v>237</v>
+        <v>299</v>
       </c>
       <c r="D50" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E50" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F50" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s">
-        <v>423</v>
+        <v>248</v>
       </c>
       <c r="C51" t="s">
-        <v>237</v>
+        <v>402</v>
       </c>
       <c r="D51" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E51" t="s">
+        <v>403</v>
+      </c>
+      <c r="F51" t="s">
+        <v>251</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="F51" t="s">
-        <v>425</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>425</v>
+      </c>
+      <c r="B52" t="s">
+        <v>426</v>
+      </c>
+      <c r="C52" t="s">
+        <v>220</v>
+      </c>
+      <c r="D52" t="s">
+        <v>174</v>
+      </c>
+      <c r="E52" t="s">
         <v>427</v>
       </c>
-      <c r="B52" t="s">
+      <c r="F52" t="s">
         <v>428</v>
       </c>
-      <c r="C52" t="s">
-        <v>237</v>
-      </c>
-      <c r="D52" t="s">
-        <v>180</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="H52" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="F52" t="s">
-        <v>430</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>430</v>
+      </c>
+      <c r="B53" t="s">
+        <v>431</v>
+      </c>
+      <c r="C53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" t="s">
+        <v>186</v>
+      </c>
+      <c r="E53" t="s">
         <v>432</v>
       </c>
-      <c r="B53" t="s">
+      <c r="F53" t="s">
         <v>433</v>
       </c>
-      <c r="C53" t="s">
-        <v>173</v>
-      </c>
-      <c r="D53" t="s">
-        <v>180</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="H53" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="F53" t="s">
-        <v>435</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>435</v>
+      </c>
+      <c r="B54" t="s">
+        <v>436</v>
+      </c>
+      <c r="C54" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" t="s">
+        <v>186</v>
+      </c>
+      <c r="E54" t="s">
         <v>437</v>
       </c>
-      <c r="B54" t="s">
-        <v>166</v>
-      </c>
-      <c r="C54" t="s">
-        <v>167</v>
-      </c>
-      <c r="D54" t="s">
-        <v>168</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>438</v>
-      </c>
-      <c r="F54" t="s">
-        <v>163</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>439</v>
@@ -4352,7 +5284,7 @@
         <v>442</v>
       </c>
       <c r="D55" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E55" t="s">
         <v>443</v>
@@ -4369,88 +5301,88 @@
         <v>446</v>
       </c>
       <c r="B56" t="s">
-        <v>363</v>
+        <v>447</v>
       </c>
       <c r="C56" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D56" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E56" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F56" t="s">
-        <v>366</v>
+        <v>450</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B57" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C57" t="s">
-        <v>452</v>
+        <v>173</v>
       </c>
       <c r="D57" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E57" t="s">
         <v>453</v>
       </c>
       <c r="F57" t="s">
+        <v>450</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>455</v>
+      </c>
+      <c r="B58" t="s">
         <v>456</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
+        <v>299</v>
+      </c>
+      <c r="D58" t="s">
+        <v>186</v>
+      </c>
+      <c r="E58" t="s">
         <v>457</v>
       </c>
-      <c r="C58" t="s">
+      <c r="F58" t="s">
         <v>458</v>
       </c>
-      <c r="D58" t="s">
-        <v>180</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="H58" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="F58" t="s">
-        <v>162</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>460</v>
+      </c>
+      <c r="B59" t="s">
         <v>461</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>462</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
+        <v>186</v>
+      </c>
+      <c r="E59" t="s">
         <v>463</v>
       </c>
-      <c r="D59" t="s">
-        <v>180</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>464</v>
-      </c>
-      <c r="F59" t="s">
-        <v>162</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>465</v>
@@ -4458,16 +5390,16 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>75</v>
+      </c>
+      <c r="B60" t="s">
         <v>466</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>467</v>
       </c>
-      <c r="C60" t="s">
-        <v>237</v>
-      </c>
       <c r="D60" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E60" t="s">
         <v>468</v>
@@ -4481,39 +5413,39 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" t="s">
         <v>471</v>
       </c>
-      <c r="B61" t="s">
-        <v>418</v>
-      </c>
       <c r="C61" t="s">
-        <v>237</v>
+        <v>472</v>
       </c>
       <c r="D61" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E61" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="F61" t="s">
-        <v>420</v>
+        <v>473</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B62" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C62" t="s">
-        <v>475</v>
+        <v>220</v>
       </c>
       <c r="D62" t="s">
-        <v>476</v>
+        <v>186</v>
       </c>
       <c r="E62" t="s">
         <v>477</v>
@@ -4530,114 +5462,1701 @@
         <v>480</v>
       </c>
       <c r="B63" t="s">
-        <v>391</v>
+        <v>481</v>
       </c>
       <c r="C63" t="s">
-        <v>481</v>
+        <v>179</v>
       </c>
       <c r="D63" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E63" t="s">
+        <v>162</v>
+      </c>
+      <c r="F63" t="s">
+        <v>162</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="F63" t="s">
-        <v>393</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>483</v>
+      </c>
+      <c r="B64" t="s">
+        <v>172</v>
+      </c>
+      <c r="C64" t="s">
+        <v>173</v>
+      </c>
+      <c r="D64" t="s">
+        <v>174</v>
+      </c>
+      <c r="E64" t="s">
         <v>484</v>
       </c>
-      <c r="B64" t="s">
+      <c r="F64" t="s">
+        <v>169</v>
+      </c>
+      <c r="H64" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="C64" t="s">
-        <v>486</v>
-      </c>
-      <c r="D64" t="s">
-        <v>180</v>
-      </c>
-      <c r="E64" t="s">
-        <v>487</v>
-      </c>
-      <c r="F64" t="s">
-        <v>488</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>486</v>
+      </c>
+      <c r="B65" t="s">
+        <v>487</v>
+      </c>
+      <c r="C65" t="s">
+        <v>488</v>
+      </c>
+      <c r="D65" t="s">
+        <v>186</v>
+      </c>
+      <c r="E65" t="s">
+        <v>489</v>
+      </c>
+      <c r="F65" t="s">
         <v>490</v>
       </c>
-      <c r="B65" t="s">
+      <c r="H65" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="C65" t="s">
-        <v>402</v>
-      </c>
-      <c r="D65" t="s">
-        <v>180</v>
-      </c>
-      <c r="E65" t="s">
-        <v>492</v>
-      </c>
-      <c r="F65" t="s">
-        <v>493</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C66" t="s">
-        <v>334</v>
+        <v>179</v>
       </c>
       <c r="D66" t="s">
-        <v>180</v>
+        <v>256</v>
       </c>
       <c r="E66" t="s">
-        <v>497</v>
+        <v>162</v>
       </c>
       <c r="F66" t="s">
-        <v>498</v>
+        <v>433</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>495</v>
+      </c>
+      <c r="B67" t="s">
+        <v>496</v>
+      </c>
+      <c r="C67" t="s">
+        <v>220</v>
+      </c>
+      <c r="D67" t="s">
+        <v>256</v>
+      </c>
+      <c r="E67" t="s">
+        <v>497</v>
+      </c>
+      <c r="F67" t="s">
+        <v>498</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>500</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B68" t="s">
+        <v>456</v>
+      </c>
+      <c r="C68" t="s">
+        <v>299</v>
+      </c>
+      <c r="D68" t="s">
+        <v>186</v>
+      </c>
+      <c r="E68" t="s">
         <v>501</v>
       </c>
-      <c r="C67" t="s">
+      <c r="F68" t="s">
         <v>502</v>
       </c>
-      <c r="D67" t="s">
-        <v>180</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="H68" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="F67" t="s">
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>504</v>
       </c>
-      <c r="H67" s="2" t="s">
+      <c r="B69" t="s">
         <v>505</v>
+      </c>
+      <c r="C69" t="s">
+        <v>506</v>
+      </c>
+      <c r="D69" t="s">
+        <v>186</v>
+      </c>
+      <c r="E69" t="s">
+        <v>507</v>
+      </c>
+      <c r="F69" t="s">
+        <v>508</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>510</v>
+      </c>
+      <c r="B70" t="s">
+        <v>511</v>
+      </c>
+      <c r="C70" t="s">
+        <v>179</v>
+      </c>
+      <c r="D70" t="s">
+        <v>186</v>
+      </c>
+      <c r="E70" t="s">
+        <v>284</v>
+      </c>
+      <c r="F70" t="s">
+        <v>512</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>514</v>
+      </c>
+      <c r="B71" t="s">
+        <v>436</v>
+      </c>
+      <c r="C71" t="s">
+        <v>179</v>
+      </c>
+      <c r="D71" t="s">
+        <v>186</v>
+      </c>
+      <c r="E71" t="s">
+        <v>515</v>
+      </c>
+      <c r="F71" t="s">
+        <v>516</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>518</v>
+      </c>
+      <c r="B72" t="s">
+        <v>519</v>
+      </c>
+      <c r="C72" t="s">
+        <v>220</v>
+      </c>
+      <c r="D72" t="s">
+        <v>186</v>
+      </c>
+      <c r="E72" t="s">
+        <v>520</v>
+      </c>
+      <c r="F72" t="s">
+        <v>162</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>522</v>
+      </c>
+      <c r="B73" t="s">
+        <v>519</v>
+      </c>
+      <c r="C73" t="s">
+        <v>220</v>
+      </c>
+      <c r="D73" t="s">
+        <v>186</v>
+      </c>
+      <c r="E73" t="s">
+        <v>523</v>
+      </c>
+      <c r="F73" t="s">
+        <v>162</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>525</v>
+      </c>
+      <c r="B74" t="s">
+        <v>526</v>
+      </c>
+      <c r="C74" t="s">
+        <v>527</v>
+      </c>
+      <c r="D74" t="s">
+        <v>186</v>
+      </c>
+      <c r="E74" t="s">
+        <v>528</v>
+      </c>
+      <c r="F74" t="s">
+        <v>529</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>531</v>
+      </c>
+      <c r="B75" t="s">
+        <v>532</v>
+      </c>
+      <c r="C75" t="s">
+        <v>299</v>
+      </c>
+      <c r="D75" t="s">
+        <v>186</v>
+      </c>
+      <c r="E75" t="s">
+        <v>533</v>
+      </c>
+      <c r="F75" t="s">
+        <v>320</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>535</v>
+      </c>
+      <c r="B76" t="s">
+        <v>536</v>
+      </c>
+      <c r="C76" t="s">
+        <v>537</v>
+      </c>
+      <c r="D76" t="s">
+        <v>186</v>
+      </c>
+      <c r="E76" t="s">
+        <v>533</v>
+      </c>
+      <c r="F76" t="s">
+        <v>538</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>540</v>
+      </c>
+      <c r="B77" t="s">
+        <v>541</v>
+      </c>
+      <c r="C77" t="s">
+        <v>192</v>
+      </c>
+      <c r="D77" t="s">
+        <v>186</v>
+      </c>
+      <c r="E77" t="s">
+        <v>542</v>
+      </c>
+      <c r="F77" t="s">
+        <v>543</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>545</v>
+      </c>
+      <c r="B78" t="s">
+        <v>546</v>
+      </c>
+      <c r="C78" t="s">
+        <v>547</v>
+      </c>
+      <c r="D78" t="s">
+        <v>186</v>
+      </c>
+      <c r="E78" t="s">
+        <v>548</v>
+      </c>
+      <c r="F78" t="s">
+        <v>549</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>551</v>
+      </c>
+      <c r="B79" t="s">
+        <v>552</v>
+      </c>
+      <c r="C79" t="s">
+        <v>220</v>
+      </c>
+      <c r="D79" t="s">
+        <v>186</v>
+      </c>
+      <c r="E79" t="s">
+        <v>553</v>
+      </c>
+      <c r="F79" t="s">
+        <v>554</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>556</v>
+      </c>
+      <c r="B80" t="s">
+        <v>557</v>
+      </c>
+      <c r="C80" t="s">
+        <v>558</v>
+      </c>
+      <c r="D80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E80" t="s">
+        <v>559</v>
+      </c>
+      <c r="F80" t="s">
+        <v>560</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>556</v>
+      </c>
+      <c r="B81" t="s">
+        <v>557</v>
+      </c>
+      <c r="C81" t="s">
+        <v>562</v>
+      </c>
+      <c r="D81" t="s">
+        <v>186</v>
+      </c>
+      <c r="E81" t="s">
+        <v>559</v>
+      </c>
+      <c r="F81" t="s">
+        <v>560</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>564</v>
+      </c>
+      <c r="B82" t="s">
+        <v>565</v>
+      </c>
+      <c r="C82" t="s">
+        <v>566</v>
+      </c>
+      <c r="D82" t="s">
+        <v>174</v>
+      </c>
+      <c r="E82" t="s">
+        <v>567</v>
+      </c>
+      <c r="F82" t="s">
+        <v>568</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>570</v>
+      </c>
+      <c r="B83" t="s">
+        <v>571</v>
+      </c>
+      <c r="C83" t="s">
+        <v>232</v>
+      </c>
+      <c r="D83" t="s">
+        <v>186</v>
+      </c>
+      <c r="E83" t="s">
+        <v>572</v>
+      </c>
+      <c r="F83" t="s">
+        <v>573</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>575</v>
+      </c>
+      <c r="B84" t="s">
+        <v>576</v>
+      </c>
+      <c r="C84" t="s">
+        <v>577</v>
+      </c>
+      <c r="D84" t="s">
+        <v>186</v>
+      </c>
+      <c r="E84" t="s">
+        <v>578</v>
+      </c>
+      <c r="F84" t="s">
+        <v>579</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>581</v>
+      </c>
+      <c r="B85" t="s">
+        <v>582</v>
+      </c>
+      <c r="C85" t="s">
+        <v>583</v>
+      </c>
+      <c r="D85" t="s">
+        <v>186</v>
+      </c>
+      <c r="E85" t="s">
+        <v>584</v>
+      </c>
+      <c r="F85" t="s">
+        <v>585</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>587</v>
+      </c>
+      <c r="B86" t="s">
+        <v>588</v>
+      </c>
+      <c r="C86" t="s">
+        <v>379</v>
+      </c>
+      <c r="D86" t="s">
+        <v>186</v>
+      </c>
+      <c r="E86" t="s">
+        <v>589</v>
+      </c>
+      <c r="F86" t="s">
+        <v>590</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>592</v>
+      </c>
+      <c r="B87" t="s">
+        <v>576</v>
+      </c>
+      <c r="C87" t="s">
+        <v>577</v>
+      </c>
+      <c r="D87" t="s">
+        <v>186</v>
+      </c>
+      <c r="E87" t="s">
+        <v>593</v>
+      </c>
+      <c r="F87" t="s">
+        <v>579</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>595</v>
+      </c>
+      <c r="B88" t="s">
+        <v>596</v>
+      </c>
+      <c r="C88" t="s">
+        <v>179</v>
+      </c>
+      <c r="D88" t="s">
+        <v>186</v>
+      </c>
+      <c r="E88" t="s">
+        <v>597</v>
+      </c>
+      <c r="F88" t="s">
+        <v>598</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>600</v>
+      </c>
+      <c r="B89" t="s">
+        <v>358</v>
+      </c>
+      <c r="C89" t="s">
+        <v>299</v>
+      </c>
+      <c r="D89" t="s">
+        <v>186</v>
+      </c>
+      <c r="E89" t="s">
+        <v>359</v>
+      </c>
+      <c r="F89" t="s">
+        <v>360</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>602</v>
+      </c>
+      <c r="B90" t="s">
+        <v>603</v>
+      </c>
+      <c r="C90" t="s">
+        <v>604</v>
+      </c>
+      <c r="D90" t="s">
+        <v>186</v>
+      </c>
+      <c r="E90" t="s">
+        <v>198</v>
+      </c>
+      <c r="F90" t="s">
+        <v>605</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>607</v>
+      </c>
+      <c r="B91" t="s">
+        <v>608</v>
+      </c>
+      <c r="C91" t="s">
+        <v>267</v>
+      </c>
+      <c r="D91" t="s">
+        <v>186</v>
+      </c>
+      <c r="E91" t="s">
+        <v>609</v>
+      </c>
+      <c r="F91" t="s">
+        <v>199</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>611</v>
+      </c>
+      <c r="B92" t="s">
+        <v>612</v>
+      </c>
+      <c r="C92" t="s">
+        <v>613</v>
+      </c>
+      <c r="D92" t="s">
+        <v>186</v>
+      </c>
+      <c r="E92" t="s">
+        <v>614</v>
+      </c>
+      <c r="F92" t="s">
+        <v>615</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>617</v>
+      </c>
+      <c r="B93" t="s">
+        <v>618</v>
+      </c>
+      <c r="C93" t="s">
+        <v>226</v>
+      </c>
+      <c r="D93" t="s">
+        <v>186</v>
+      </c>
+      <c r="E93" t="s">
+        <v>619</v>
+      </c>
+      <c r="F93" t="s">
+        <v>370</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>621</v>
+      </c>
+      <c r="B94" t="s">
+        <v>622</v>
+      </c>
+      <c r="C94" t="s">
+        <v>623</v>
+      </c>
+      <c r="D94" t="s">
+        <v>624</v>
+      </c>
+      <c r="E94" t="s">
+        <v>625</v>
+      </c>
+      <c r="F94" t="s">
+        <v>626</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>628</v>
+      </c>
+      <c r="B95" t="s">
+        <v>237</v>
+      </c>
+      <c r="C95" t="s">
+        <v>220</v>
+      </c>
+      <c r="D95" t="s">
+        <v>186</v>
+      </c>
+      <c r="E95" t="s">
+        <v>629</v>
+      </c>
+      <c r="F95" t="s">
+        <v>239</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>631</v>
+      </c>
+      <c r="B96" t="s">
+        <v>632</v>
+      </c>
+      <c r="C96" t="s">
+        <v>633</v>
+      </c>
+      <c r="D96" t="s">
+        <v>186</v>
+      </c>
+      <c r="E96" t="s">
+        <v>634</v>
+      </c>
+      <c r="F96" t="s">
+        <v>162</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>636</v>
+      </c>
+      <c r="B97" t="s">
+        <v>637</v>
+      </c>
+      <c r="C97" t="s">
+        <v>220</v>
+      </c>
+      <c r="D97" t="s">
+        <v>186</v>
+      </c>
+      <c r="E97" t="s">
+        <v>278</v>
+      </c>
+      <c r="F97" t="s">
+        <v>638</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>636</v>
+      </c>
+      <c r="B98" t="s">
+        <v>640</v>
+      </c>
+      <c r="C98" t="s">
+        <v>641</v>
+      </c>
+      <c r="D98" t="s">
+        <v>186</v>
+      </c>
+      <c r="E98" t="s">
+        <v>642</v>
+      </c>
+      <c r="F98" t="s">
+        <v>643</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>645</v>
+      </c>
+      <c r="B99" t="s">
+        <v>646</v>
+      </c>
+      <c r="C99" t="s">
+        <v>647</v>
+      </c>
+      <c r="D99" t="s">
+        <v>186</v>
+      </c>
+      <c r="E99" t="s">
+        <v>162</v>
+      </c>
+      <c r="F99" t="s">
+        <v>648</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>645</v>
+      </c>
+      <c r="B100" t="s">
+        <v>646</v>
+      </c>
+      <c r="C100" t="s">
+        <v>650</v>
+      </c>
+      <c r="D100" t="s">
+        <v>186</v>
+      </c>
+      <c r="E100" t="s">
+        <v>162</v>
+      </c>
+      <c r="F100" t="s">
+        <v>648</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>645</v>
+      </c>
+      <c r="B101" t="s">
+        <v>646</v>
+      </c>
+      <c r="C101" t="s">
+        <v>334</v>
+      </c>
+      <c r="D101" t="s">
+        <v>186</v>
+      </c>
+      <c r="E101" t="s">
+        <v>162</v>
+      </c>
+      <c r="F101" t="s">
+        <v>648</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>653</v>
+      </c>
+      <c r="B102" t="s">
+        <v>456</v>
+      </c>
+      <c r="C102" t="s">
+        <v>654</v>
+      </c>
+      <c r="D102" t="s">
+        <v>186</v>
+      </c>
+      <c r="E102" t="s">
+        <v>655</v>
+      </c>
+      <c r="F102" t="s">
+        <v>656</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>658</v>
+      </c>
+      <c r="B103" t="s">
+        <v>659</v>
+      </c>
+      <c r="C103" t="s">
+        <v>192</v>
+      </c>
+      <c r="D103" t="s">
+        <v>186</v>
+      </c>
+      <c r="E103" t="s">
+        <v>660</v>
+      </c>
+      <c r="F103" t="s">
+        <v>661</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>663</v>
+      </c>
+      <c r="B104" t="s">
+        <v>632</v>
+      </c>
+      <c r="C104" t="s">
+        <v>179</v>
+      </c>
+      <c r="D104" t="s">
+        <v>186</v>
+      </c>
+      <c r="E104" t="s">
+        <v>664</v>
+      </c>
+      <c r="F104" t="s">
+        <v>162</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>666</v>
+      </c>
+      <c r="B105" t="s">
+        <v>632</v>
+      </c>
+      <c r="C105" t="s">
+        <v>179</v>
+      </c>
+      <c r="D105" t="s">
+        <v>186</v>
+      </c>
+      <c r="E105" t="s">
+        <v>667</v>
+      </c>
+      <c r="F105" t="s">
+        <v>162</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>669</v>
+      </c>
+      <c r="B106" t="s">
+        <v>670</v>
+      </c>
+      <c r="C106" t="s">
+        <v>243</v>
+      </c>
+      <c r="D106" t="s">
+        <v>186</v>
+      </c>
+      <c r="E106" t="s">
+        <v>671</v>
+      </c>
+      <c r="F106" t="s">
+        <v>672</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>674</v>
+      </c>
+      <c r="B107" t="s">
+        <v>675</v>
+      </c>
+      <c r="C107" t="s">
+        <v>676</v>
+      </c>
+      <c r="D107" t="s">
+        <v>186</v>
+      </c>
+      <c r="E107" t="s">
+        <v>677</v>
+      </c>
+      <c r="F107" t="s">
+        <v>678</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>680</v>
+      </c>
+      <c r="B108" t="s">
+        <v>681</v>
+      </c>
+      <c r="C108" t="s">
+        <v>220</v>
+      </c>
+      <c r="D108" t="s">
+        <v>186</v>
+      </c>
+      <c r="E108" t="s">
+        <v>682</v>
+      </c>
+      <c r="F108" t="s">
+        <v>683</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>685</v>
+      </c>
+      <c r="B109" t="s">
+        <v>248</v>
+      </c>
+      <c r="C109" t="s">
+        <v>249</v>
+      </c>
+      <c r="D109" t="s">
+        <v>186</v>
+      </c>
+      <c r="E109" t="s">
+        <v>250</v>
+      </c>
+      <c r="F109" t="s">
+        <v>251</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>687</v>
+      </c>
+      <c r="B110" t="s">
+        <v>688</v>
+      </c>
+      <c r="C110" t="s">
+        <v>220</v>
+      </c>
+      <c r="D110" t="s">
+        <v>186</v>
+      </c>
+      <c r="E110" t="s">
+        <v>689</v>
+      </c>
+      <c r="F110" t="s">
+        <v>690</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>692</v>
+      </c>
+      <c r="B111" t="s">
+        <v>693</v>
+      </c>
+      <c r="C111" t="s">
+        <v>220</v>
+      </c>
+      <c r="D111" t="s">
+        <v>186</v>
+      </c>
+      <c r="E111" t="s">
+        <v>694</v>
+      </c>
+      <c r="F111" t="s">
+        <v>695</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>697</v>
+      </c>
+      <c r="B112" t="s">
+        <v>698</v>
+      </c>
+      <c r="C112" t="s">
+        <v>179</v>
+      </c>
+      <c r="D112" t="s">
+        <v>186</v>
+      </c>
+      <c r="E112" t="s">
+        <v>699</v>
+      </c>
+      <c r="F112" t="s">
+        <v>700</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>702</v>
+      </c>
+      <c r="B113" t="s">
+        <v>703</v>
+      </c>
+      <c r="C113" t="s">
+        <v>267</v>
+      </c>
+      <c r="D113" t="s">
+        <v>256</v>
+      </c>
+      <c r="E113" t="s">
+        <v>704</v>
+      </c>
+      <c r="F113" t="s">
+        <v>538</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>706</v>
+      </c>
+      <c r="B114" t="s">
+        <v>172</v>
+      </c>
+      <c r="C114" t="s">
+        <v>173</v>
+      </c>
+      <c r="D114" t="s">
+        <v>174</v>
+      </c>
+      <c r="E114" t="s">
+        <v>707</v>
+      </c>
+      <c r="F114" t="s">
+        <v>169</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>709</v>
+      </c>
+      <c r="B115" t="s">
+        <v>710</v>
+      </c>
+      <c r="C115" t="s">
+        <v>442</v>
+      </c>
+      <c r="D115" t="s">
+        <v>186</v>
+      </c>
+      <c r="E115" t="s">
+        <v>711</v>
+      </c>
+      <c r="F115" t="s">
+        <v>712</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>714</v>
+      </c>
+      <c r="B116" t="s">
+        <v>632</v>
+      </c>
+      <c r="C116" t="s">
+        <v>633</v>
+      </c>
+      <c r="D116" t="s">
+        <v>186</v>
+      </c>
+      <c r="E116" t="s">
+        <v>667</v>
+      </c>
+      <c r="F116" t="s">
+        <v>162</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>716</v>
+      </c>
+      <c r="B117" t="s">
+        <v>717</v>
+      </c>
+      <c r="C117" t="s">
+        <v>154</v>
+      </c>
+      <c r="D117" t="s">
+        <v>256</v>
+      </c>
+      <c r="E117" t="s">
+        <v>718</v>
+      </c>
+      <c r="F117" t="s">
+        <v>719</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>721</v>
+      </c>
+      <c r="B118" t="s">
+        <v>582</v>
+      </c>
+      <c r="C118" t="s">
+        <v>722</v>
+      </c>
+      <c r="D118" t="s">
+        <v>186</v>
+      </c>
+      <c r="E118" t="s">
+        <v>723</v>
+      </c>
+      <c r="F118" t="s">
+        <v>585</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>725</v>
+      </c>
+      <c r="B119" t="s">
+        <v>726</v>
+      </c>
+      <c r="C119" t="s">
+        <v>727</v>
+      </c>
+      <c r="D119" t="s">
+        <v>186</v>
+      </c>
+      <c r="E119" t="s">
+        <v>728</v>
+      </c>
+      <c r="F119" t="s">
+        <v>729</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>731</v>
+      </c>
+      <c r="B120" t="s">
+        <v>732</v>
+      </c>
+      <c r="C120" t="s">
+        <v>733</v>
+      </c>
+      <c r="D120" t="s">
+        <v>186</v>
+      </c>
+      <c r="E120" t="s">
+        <v>734</v>
+      </c>
+      <c r="F120" t="s">
+        <v>162</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>736</v>
+      </c>
+      <c r="B121" t="s">
+        <v>737</v>
+      </c>
+      <c r="C121" t="s">
+        <v>267</v>
+      </c>
+      <c r="D121" t="s">
+        <v>186</v>
+      </c>
+      <c r="E121" t="s">
+        <v>589</v>
+      </c>
+      <c r="F121" t="s">
+        <v>738</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>740</v>
+      </c>
+      <c r="B122" t="s">
+        <v>741</v>
+      </c>
+      <c r="C122" t="s">
+        <v>299</v>
+      </c>
+      <c r="D122" t="s">
+        <v>186</v>
+      </c>
+      <c r="E122" t="s">
+        <v>742</v>
+      </c>
+      <c r="F122" t="s">
+        <v>743</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>745</v>
+      </c>
+      <c r="B123" t="s">
+        <v>746</v>
+      </c>
+      <c r="C123" t="s">
+        <v>299</v>
+      </c>
+      <c r="D123" t="s">
+        <v>186</v>
+      </c>
+      <c r="E123" t="s">
+        <v>747</v>
+      </c>
+      <c r="F123" t="s">
+        <v>748</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>750</v>
+      </c>
+      <c r="B124" t="s">
+        <v>751</v>
+      </c>
+      <c r="C124" t="s">
+        <v>472</v>
+      </c>
+      <c r="D124" t="s">
+        <v>186</v>
+      </c>
+      <c r="E124" t="s">
+        <v>752</v>
+      </c>
+      <c r="F124" t="s">
+        <v>162</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>754</v>
+      </c>
+      <c r="B125" t="s">
+        <v>755</v>
+      </c>
+      <c r="C125" t="s">
+        <v>220</v>
+      </c>
+      <c r="D125" t="s">
+        <v>186</v>
+      </c>
+      <c r="E125" t="s">
+        <v>756</v>
+      </c>
+      <c r="F125" t="s">
+        <v>757</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>754</v>
+      </c>
+      <c r="B126" t="s">
+        <v>737</v>
+      </c>
+      <c r="C126" t="s">
+        <v>267</v>
+      </c>
+      <c r="D126" t="s">
+        <v>186</v>
+      </c>
+      <c r="E126" t="s">
+        <v>759</v>
+      </c>
+      <c r="F126" t="s">
+        <v>760</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>762</v>
+      </c>
+      <c r="B127" t="s">
+        <v>763</v>
+      </c>
+      <c r="C127" t="s">
+        <v>299</v>
+      </c>
+      <c r="D127" t="s">
+        <v>186</v>
+      </c>
+      <c r="E127" t="s">
+        <v>764</v>
+      </c>
+      <c r="F127" t="s">
+        <v>765</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>767</v>
+      </c>
+      <c r="B128" t="s">
+        <v>681</v>
+      </c>
+      <c r="C128" t="s">
+        <v>220</v>
+      </c>
+      <c r="D128" t="s">
+        <v>186</v>
+      </c>
+      <c r="E128" t="s">
+        <v>682</v>
+      </c>
+      <c r="F128" t="s">
+        <v>683</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>769</v>
+      </c>
+      <c r="B129" t="s">
+        <v>770</v>
+      </c>
+      <c r="C129" t="s">
+        <v>771</v>
+      </c>
+      <c r="D129" t="s">
+        <v>624</v>
+      </c>
+      <c r="E129" t="s">
+        <v>772</v>
+      </c>
+      <c r="F129" t="s">
+        <v>773</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>775</v>
+      </c>
+      <c r="B130" t="s">
+        <v>776</v>
+      </c>
+      <c r="C130" t="s">
+        <v>283</v>
+      </c>
+      <c r="D130" t="s">
+        <v>186</v>
+      </c>
+      <c r="E130" t="s">
+        <v>777</v>
+      </c>
+      <c r="F130" t="s">
+        <v>778</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>780</v>
+      </c>
+      <c r="B131" t="s">
+        <v>781</v>
+      </c>
+      <c r="C131" t="s">
+        <v>527</v>
+      </c>
+      <c r="D131" t="s">
+        <v>186</v>
+      </c>
+      <c r="E131" t="s">
+        <v>198</v>
+      </c>
+      <c r="F131" t="s">
+        <v>782</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>784</v>
+      </c>
+      <c r="B132" t="s">
+        <v>237</v>
+      </c>
+      <c r="C132" t="s">
+        <v>623</v>
+      </c>
+      <c r="D132" t="s">
+        <v>186</v>
+      </c>
+      <c r="E132" t="s">
+        <v>785</v>
+      </c>
+      <c r="F132" t="s">
+        <v>239</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>787</v>
+      </c>
+      <c r="B133" t="s">
+        <v>788</v>
+      </c>
+      <c r="C133" t="s">
+        <v>789</v>
+      </c>
+      <c r="D133" t="s">
+        <v>186</v>
+      </c>
+      <c r="E133" t="s">
+        <v>790</v>
+      </c>
+      <c r="F133" t="s">
+        <v>791</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>793</v>
+      </c>
+      <c r="B134" t="s">
+        <v>794</v>
+      </c>
+      <c r="C134" t="s">
+        <v>192</v>
+      </c>
+      <c r="D134" t="s">
+        <v>186</v>
+      </c>
+      <c r="E134" t="s">
+        <v>795</v>
+      </c>
+      <c r="F134" t="s">
+        <v>796</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>798</v>
+      </c>
+      <c r="B135" t="s">
+        <v>799</v>
+      </c>
+      <c r="C135" t="s">
+        <v>527</v>
+      </c>
+      <c r="D135" t="s">
+        <v>186</v>
+      </c>
+      <c r="E135" t="s">
+        <v>800</v>
+      </c>
+      <c r="F135" t="s">
+        <v>801</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>803</v>
+      </c>
+      <c r="B136" t="s">
+        <v>804</v>
+      </c>
+      <c r="C136" t="s">
+        <v>805</v>
+      </c>
+      <c r="D136" t="s">
+        <v>186</v>
+      </c>
+      <c r="E136" t="s">
+        <v>806</v>
+      </c>
+      <c r="F136" t="s">
+        <v>807</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -4709,6 +7228,75 @@
     <hyperlink ref="H65" r:id="rId64"/>
     <hyperlink ref="H66" r:id="rId65"/>
     <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4758,13 +7346,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>506</v>
+        <v>809</v>
       </c>
       <c r="B2" t="s">
-        <v>507</v>
+        <v>810</v>
       </c>
       <c r="C2" t="s">
-        <v>508</v>
+        <v>811</v>
       </c>
       <c r="D2" t="s">
         <v>162</v>
@@ -4773,21 +7361,21 @@
         <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>510</v>
+        <v>813</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>511</v>
+        <v>814</v>
       </c>
       <c r="B3" t="s">
-        <v>507</v>
+        <v>810</v>
       </c>
       <c r="C3" t="s">
-        <v>512</v>
+        <v>815</v>
       </c>
       <c r="D3" t="s">
         <v>162</v>
@@ -4796,21 +7384,21 @@
         <v>162</v>
       </c>
       <c r="F3" t="s">
-        <v>513</v>
+        <v>816</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>514</v>
+        <v>817</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>515</v>
+        <v>818</v>
       </c>
       <c r="B4" t="s">
-        <v>516</v>
+        <v>819</v>
       </c>
       <c r="C4" t="s">
-        <v>517</v>
+        <v>820</v>
       </c>
       <c r="D4" t="s">
         <v>162</v>
@@ -4819,21 +7407,21 @@
         <v>162</v>
       </c>
       <c r="F4" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>518</v>
+        <v>821</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>519</v>
+        <v>822</v>
       </c>
       <c r="B5" t="s">
-        <v>520</v>
+        <v>823</v>
       </c>
       <c r="C5" t="s">
-        <v>521</v>
+        <v>824</v>
       </c>
       <c r="D5" t="s">
         <v>162</v>
@@ -4842,21 +7430,21 @@
         <v>162</v>
       </c>
       <c r="F5" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>522</v>
+        <v>825</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>523</v>
+        <v>826</v>
       </c>
       <c r="B6" t="s">
-        <v>524</v>
+        <v>827</v>
       </c>
       <c r="C6" t="s">
-        <v>525</v>
+        <v>828</v>
       </c>
       <c r="D6" t="s">
         <v>162</v>
@@ -4865,21 +7453,21 @@
         <v>162</v>
       </c>
       <c r="F6" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>526</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>527</v>
+        <v>830</v>
       </c>
       <c r="B7" t="s">
-        <v>528</v>
+        <v>831</v>
       </c>
       <c r="C7" t="s">
-        <v>529</v>
+        <v>832</v>
       </c>
       <c r="D7" t="s">
         <v>162</v>
@@ -4888,21 +7476,21 @@
         <v>162</v>
       </c>
       <c r="F7" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>530</v>
+        <v>833</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>531</v>
+        <v>834</v>
       </c>
       <c r="B8" t="s">
-        <v>532</v>
+        <v>835</v>
       </c>
       <c r="C8" t="s">
-        <v>533</v>
+        <v>836</v>
       </c>
       <c r="D8" t="s">
         <v>162</v>
@@ -4911,21 +7499,21 @@
         <v>162</v>
       </c>
       <c r="F8" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>534</v>
+        <v>837</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>535</v>
+        <v>838</v>
       </c>
       <c r="B9" t="s">
-        <v>536</v>
+        <v>839</v>
       </c>
       <c r="C9" t="s">
-        <v>537</v>
+        <v>840</v>
       </c>
       <c r="D9" t="s">
         <v>162</v>
@@ -4934,21 +7522,21 @@
         <v>162</v>
       </c>
       <c r="F9" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>538</v>
+        <v>841</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>539</v>
+        <v>842</v>
       </c>
       <c r="B10" t="s">
-        <v>540</v>
+        <v>843</v>
       </c>
       <c r="C10" t="s">
-        <v>541</v>
+        <v>844</v>
       </c>
       <c r="D10" t="s">
         <v>162</v>
@@ -4957,21 +7545,21 @@
         <v>162</v>
       </c>
       <c r="F10" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>542</v>
+        <v>845</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>543</v>
+        <v>846</v>
       </c>
       <c r="B11" t="s">
-        <v>544</v>
+        <v>847</v>
       </c>
       <c r="C11" t="s">
-        <v>545</v>
+        <v>848</v>
       </c>
       <c r="D11" t="s">
         <v>162</v>
@@ -4980,21 +7568,21 @@
         <v>162</v>
       </c>
       <c r="F11" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>546</v>
+        <v>849</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>547</v>
+        <v>850</v>
       </c>
       <c r="B12" t="s">
-        <v>548</v>
+        <v>851</v>
       </c>
       <c r="C12" t="s">
-        <v>549</v>
+        <v>852</v>
       </c>
       <c r="D12" t="s">
         <v>162</v>
@@ -5003,21 +7591,21 @@
         <v>162</v>
       </c>
       <c r="F12" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>550</v>
+        <v>853</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>551</v>
+        <v>854</v>
       </c>
       <c r="B13" t="s">
-        <v>552</v>
+        <v>855</v>
       </c>
       <c r="C13" t="s">
-        <v>304</v>
+        <v>488</v>
       </c>
       <c r="D13" t="s">
         <v>162</v>
@@ -5026,21 +7614,21 @@
         <v>162</v>
       </c>
       <c r="F13" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>553</v>
+        <v>856</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>554</v>
+        <v>857</v>
       </c>
       <c r="B14" t="s">
-        <v>555</v>
+        <v>858</v>
       </c>
       <c r="C14" t="s">
-        <v>556</v>
+        <v>859</v>
       </c>
       <c r="D14" t="s">
         <v>162</v>
@@ -5049,21 +7637,21 @@
         <v>162</v>
       </c>
       <c r="F14" t="s">
-        <v>513</v>
+        <v>816</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>557</v>
+        <v>860</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>558</v>
+        <v>861</v>
       </c>
       <c r="B15" t="s">
-        <v>559</v>
+        <v>862</v>
       </c>
       <c r="C15" t="s">
-        <v>560</v>
+        <v>863</v>
       </c>
       <c r="D15" t="s">
         <v>162</v>
@@ -5072,21 +7660,21 @@
         <v>162</v>
       </c>
       <c r="F15" t="s">
-        <v>561</v>
+        <v>864</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>562</v>
+        <v>865</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>563</v>
+        <v>866</v>
       </c>
       <c r="B16" t="s">
-        <v>564</v>
+        <v>867</v>
       </c>
       <c r="C16" t="s">
-        <v>565</v>
+        <v>868</v>
       </c>
       <c r="D16" t="s">
         <v>162</v>
@@ -5095,21 +7683,21 @@
         <v>162</v>
       </c>
       <c r="F16" t="s">
-        <v>566</v>
+        <v>869</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>567</v>
+        <v>870</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>568</v>
+        <v>871</v>
       </c>
       <c r="B17" t="s">
-        <v>569</v>
+        <v>872</v>
       </c>
       <c r="C17" t="s">
-        <v>242</v>
+        <v>334</v>
       </c>
       <c r="D17" t="s">
         <v>162</v>
@@ -5118,21 +7706,21 @@
         <v>162</v>
       </c>
       <c r="F17" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>570</v>
+        <v>873</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>571</v>
+        <v>874</v>
       </c>
       <c r="B18" t="s">
-        <v>572</v>
+        <v>875</v>
       </c>
       <c r="C18" t="s">
-        <v>573</v>
+        <v>876</v>
       </c>
       <c r="D18" t="s">
         <v>162</v>
@@ -5141,21 +7729,21 @@
         <v>162</v>
       </c>
       <c r="F18" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>574</v>
+        <v>877</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>575</v>
+        <v>878</v>
       </c>
       <c r="B19" t="s">
-        <v>576</v>
+        <v>879</v>
       </c>
       <c r="C19" t="s">
-        <v>577</v>
+        <v>880</v>
       </c>
       <c r="D19" t="s">
         <v>162</v>
@@ -5164,21 +7752,21 @@
         <v>162</v>
       </c>
       <c r="F19" t="s">
-        <v>513</v>
+        <v>816</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>578</v>
+        <v>881</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>579</v>
+        <v>882</v>
       </c>
       <c r="B20" t="s">
-        <v>580</v>
+        <v>883</v>
       </c>
       <c r="C20" t="s">
-        <v>581</v>
+        <v>884</v>
       </c>
       <c r="D20" t="s">
         <v>162</v>
@@ -5187,21 +7775,21 @@
         <v>162</v>
       </c>
       <c r="F20" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>582</v>
+        <v>885</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>583</v>
+        <v>886</v>
       </c>
       <c r="B21" t="s">
-        <v>584</v>
+        <v>887</v>
       </c>
       <c r="C21" t="s">
-        <v>585</v>
+        <v>888</v>
       </c>
       <c r="D21" t="s">
         <v>162</v>
@@ -5210,21 +7798,21 @@
         <v>162</v>
       </c>
       <c r="F21" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>586</v>
+        <v>889</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>587</v>
+        <v>890</v>
       </c>
       <c r="B22" t="s">
-        <v>588</v>
+        <v>891</v>
       </c>
       <c r="C22" t="s">
-        <v>589</v>
+        <v>892</v>
       </c>
       <c r="D22" t="s">
         <v>162</v>
@@ -5233,21 +7821,21 @@
         <v>162</v>
       </c>
       <c r="F22" t="s">
-        <v>513</v>
+        <v>816</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>590</v>
+        <v>893</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>591</v>
+        <v>894</v>
       </c>
       <c r="B23" t="s">
-        <v>592</v>
+        <v>895</v>
       </c>
       <c r="C23" t="s">
-        <v>593</v>
+        <v>896</v>
       </c>
       <c r="D23" t="s">
         <v>162</v>
@@ -5256,21 +7844,21 @@
         <v>162</v>
       </c>
       <c r="F23" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>594</v>
+        <v>897</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>595</v>
+        <v>898</v>
       </c>
       <c r="B24" t="s">
-        <v>596</v>
+        <v>899</v>
       </c>
       <c r="C24" t="s">
-        <v>560</v>
+        <v>863</v>
       </c>
       <c r="D24" t="s">
         <v>162</v>
@@ -5279,21 +7867,21 @@
         <v>162</v>
       </c>
       <c r="F24" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>597</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>598</v>
+        <v>901</v>
       </c>
       <c r="B25" t="s">
-        <v>599</v>
+        <v>902</v>
       </c>
       <c r="C25" t="s">
-        <v>600</v>
+        <v>903</v>
       </c>
       <c r="D25" t="s">
         <v>162</v>
@@ -5302,21 +7890,21 @@
         <v>162</v>
       </c>
       <c r="F25" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>601</v>
+        <v>904</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>602</v>
+        <v>905</v>
       </c>
       <c r="B26" t="s">
-        <v>548</v>
+        <v>851</v>
       </c>
       <c r="C26" t="s">
-        <v>549</v>
+        <v>852</v>
       </c>
       <c r="D26" t="s">
         <v>162</v>
@@ -5325,21 +7913,21 @@
         <v>162</v>
       </c>
       <c r="F26" t="s">
-        <v>513</v>
+        <v>816</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>603</v>
+        <v>906</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>604</v>
+        <v>907</v>
       </c>
       <c r="B27" t="s">
-        <v>507</v>
+        <v>810</v>
       </c>
       <c r="C27" t="s">
-        <v>605</v>
+        <v>908</v>
       </c>
       <c r="D27" t="s">
         <v>162</v>
@@ -5348,21 +7936,21 @@
         <v>162</v>
       </c>
       <c r="F27" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>606</v>
+        <v>909</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>607</v>
+        <v>910</v>
       </c>
       <c r="B28" t="s">
-        <v>608</v>
+        <v>911</v>
       </c>
       <c r="C28" t="s">
-        <v>541</v>
+        <v>844</v>
       </c>
       <c r="D28" t="s">
         <v>162</v>
@@ -5371,21 +7959,21 @@
         <v>162</v>
       </c>
       <c r="F28" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>609</v>
+        <v>912</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>610</v>
+        <v>913</v>
       </c>
       <c r="B29" t="s">
-        <v>611</v>
+        <v>914</v>
       </c>
       <c r="C29" t="s">
-        <v>612</v>
+        <v>915</v>
       </c>
       <c r="D29" t="s">
         <v>162</v>
@@ -5394,21 +7982,21 @@
         <v>162</v>
       </c>
       <c r="F29" t="s">
-        <v>613</v>
+        <v>916</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>614</v>
+        <v>917</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>615</v>
+        <v>918</v>
       </c>
       <c r="B30" t="s">
-        <v>608</v>
+        <v>911</v>
       </c>
       <c r="C30" t="s">
-        <v>541</v>
+        <v>844</v>
       </c>
       <c r="D30" t="s">
         <v>162</v>
@@ -5417,21 +8005,21 @@
         <v>162</v>
       </c>
       <c r="F30" t="s">
-        <v>616</v>
+        <v>919</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>617</v>
+        <v>920</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>618</v>
+        <v>921</v>
       </c>
       <c r="B31" t="s">
-        <v>619</v>
+        <v>922</v>
       </c>
       <c r="C31" t="s">
-        <v>620</v>
+        <v>633</v>
       </c>
       <c r="D31" t="s">
         <v>162</v>
@@ -5440,21 +8028,21 @@
         <v>162</v>
       </c>
       <c r="F31" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>621</v>
+        <v>923</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>622</v>
+        <v>924</v>
       </c>
       <c r="B32" t="s">
-        <v>623</v>
+        <v>925</v>
       </c>
       <c r="C32" t="s">
-        <v>624</v>
+        <v>926</v>
       </c>
       <c r="D32" t="s">
         <v>162</v>
@@ -5463,21 +8051,21 @@
         <v>162</v>
       </c>
       <c r="F32" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>625</v>
+        <v>927</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>626</v>
+        <v>928</v>
       </c>
       <c r="B33" t="s">
-        <v>627</v>
+        <v>929</v>
       </c>
       <c r="C33" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="D33" t="s">
         <v>162</v>
@@ -5486,21 +8074,21 @@
         <v>162</v>
       </c>
       <c r="F33" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>628</v>
+        <v>930</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>629</v>
+        <v>931</v>
       </c>
       <c r="B34" t="s">
-        <v>630</v>
+        <v>932</v>
       </c>
       <c r="C34" t="s">
-        <v>631</v>
+        <v>933</v>
       </c>
       <c r="D34" t="s">
         <v>162</v>
@@ -5509,21 +8097,21 @@
         <v>162</v>
       </c>
       <c r="F34" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>632</v>
+        <v>934</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>633</v>
+        <v>935</v>
       </c>
       <c r="B35" t="s">
-        <v>569</v>
+        <v>872</v>
       </c>
       <c r="C35" t="s">
-        <v>242</v>
+        <v>334</v>
       </c>
       <c r="D35" t="s">
         <v>162</v>
@@ -5532,21 +8120,21 @@
         <v>162</v>
       </c>
       <c r="F35" t="s">
-        <v>509</v>
+        <v>812</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>634</v>
+        <v>936</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>635</v>
+        <v>937</v>
       </c>
       <c r="B36" t="s">
-        <v>636</v>
+        <v>938</v>
       </c>
       <c r="C36" t="s">
-        <v>541</v>
+        <v>844</v>
       </c>
       <c r="D36" t="s">
         <v>162</v>
@@ -5555,21 +8143,21 @@
         <v>162</v>
       </c>
       <c r="F36" t="s">
-        <v>613</v>
+        <v>916</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>637</v>
+        <v>939</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>638</v>
+        <v>940</v>
       </c>
       <c r="B37" t="s">
-        <v>639</v>
+        <v>941</v>
       </c>
       <c r="C37" t="s">
-        <v>640</v>
+        <v>942</v>
       </c>
       <c r="D37" t="s">
         <v>162</v>
@@ -5578,21 +8166,21 @@
         <v>162</v>
       </c>
       <c r="F37" t="s">
-        <v>641</v>
+        <v>943</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>642</v>
+        <v>944</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>643</v>
+        <v>945</v>
       </c>
       <c r="B38" t="s">
-        <v>540</v>
+        <v>843</v>
       </c>
       <c r="C38" t="s">
-        <v>644</v>
+        <v>946</v>
       </c>
       <c r="D38" t="s">
         <v>162</v>
@@ -5601,10 +8189,10 @@
         <v>162</v>
       </c>
       <c r="F38" t="s">
-        <v>613</v>
+        <v>916</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>645</v>
+        <v>947</v>
       </c>
     </row>
   </sheetData>
